--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12200"/>
+    <workbookView windowWidth="30720" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>一级菜单</t>
   </si>
@@ -47,133 +47,361 @@
     <t>主数据</t>
   </si>
   <si>
-    <t>供应商</t>
-  </si>
-  <si>
-    <t>客户</t>
+    <t>供应商管理</t>
+  </si>
+  <si>
+    <t>供应商档案</t>
+  </si>
+  <si>
+    <t>维护供应商档案（名称、税号、地址、联系人、银行账户）、行业、地区、分类（原材料/标准件/服务类）、资质文件上传、合作状态（启用/冻结）、历史交易记录</t>
+  </si>
+  <si>
+    <t>供应商评估</t>
+  </si>
+  <si>
+    <t>支持质量、交期、服务评分机制</t>
+  </si>
+  <si>
+    <t>客户管理</t>
+  </si>
+  <si>
+    <t>客户档案</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>管理客户基本信息、信用额度、账期、开票信息、发货地址。支持客户分级（战略</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF111133"/>
+        <rFont val="helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>普通）、销售区域划分、历史订单查询。</t>
+    </r>
+  </si>
+  <si>
+    <t>客户信用管理</t>
+  </si>
+  <si>
+    <t>设置信用额度与账期控制</t>
+  </si>
+  <si>
+    <t>物料产品</t>
   </si>
   <si>
     <t>物料产品分类</t>
   </si>
   <si>
+    <t>定义物料编码规则，维护物料名称、规格型号、单位（基本/采购/销售）、分类、是否启用BOM、库存属性（是否批次/序列号管理）、默认仓库/库位、安全库存等。</t>
+  </si>
+  <si>
     <t>物料产品管理</t>
   </si>
   <si>
+    <t>定义分类原材料、成品等</t>
+  </si>
+  <si>
     <t>仓库设置</t>
   </si>
   <si>
-    <t>仓库、库区、库位设置</t>
+    <t>支持多级结构：公司 → 仓库 → 库区 → 库位。每个库位可绑定条码，支持PDA扫码操作。设置库位属性（如待检区、合格区、不良品区）。</t>
   </si>
   <si>
     <t>车间设置</t>
   </si>
   <si>
+    <t>定义生产车间及基本信息</t>
+  </si>
+  <si>
     <t>工作站设置</t>
   </si>
   <si>
+    <t>生产线上的具体操作工位，用于报工与排产</t>
+  </si>
+  <si>
     <t>计量单位</t>
   </si>
   <si>
+    <t>支持主单位与辅助单位换算（如1箱=20件），并可在采购、销售、生产中灵活使用。</t>
+  </si>
+  <si>
     <t>生产管理</t>
   </si>
   <si>
+    <t>生产计划</t>
+  </si>
+  <si>
+    <t>根据销售预测与订单，制定主生产计划，明确成品生产数量与时间。</t>
+  </si>
+  <si>
+    <t>物料需求计划</t>
+  </si>
+  <si>
+    <t>基于MPS和BOM展开，计算所需原材料、半成品的需求量与到料时间，生成采购建议或生产任务</t>
+  </si>
+  <si>
+    <t>产品转序卡</t>
+  </si>
+  <si>
+    <t>记录产品在各工序间的流转状态，包含工序名称、操作员、开工/完工时间、工时、产量、不良数等</t>
+  </si>
+  <si>
+    <t>材料请领</t>
+  </si>
+  <si>
+    <t>车间根据生产任务提交领料申请，仓库审核后发料。支持按BOM自动计算理论用量。</t>
+  </si>
+  <si>
+    <t>日排产计划</t>
+  </si>
+  <si>
+    <t>将生产任务细化到每日、每班、每工位，支持甘特图可视化排程，考虑设备、人力、模具等约束。</t>
+  </si>
+  <si>
+    <t>生产报工</t>
+  </si>
+  <si>
+    <t>操作员通过PC或手机端扫码报工，记录实际产量、工时、物料消耗。支持反冲料功能。</t>
+  </si>
+  <si>
+    <t>生产成品入库</t>
+  </si>
+  <si>
+    <t>生产完成后提交质检，合格后办理成品入库，关联生产订单与批次信息。</t>
+  </si>
+  <si>
+    <t>委外加工</t>
+  </si>
+  <si>
+    <t>管理外协加工全过程：发料 → 加工 → 回货检验 → 入库 → 结算加工费。</t>
+  </si>
+  <si>
+    <t>销售管理</t>
+  </si>
+  <si>
     <t>客户订单</t>
   </si>
   <si>
-    <t>生产计划</t>
-  </si>
-  <si>
-    <t>材料进厂</t>
-  </si>
-  <si>
-    <t>产品转序卡</t>
-  </si>
-  <si>
-    <t>材料请领</t>
-  </si>
-  <si>
-    <t>日排产计划</t>
-  </si>
-  <si>
-    <t>生产成品入库</t>
-  </si>
-  <si>
-    <t>委外加工</t>
-  </si>
-  <si>
-    <t>销售管理</t>
-  </si>
-  <si>
-    <t>产成品出入库</t>
+    <t>外部订单；接收客户销售订单，作为MPS输入。支持订单评审（交期、产能、物料 availability）。</t>
+  </si>
+  <si>
+    <t>订单转化</t>
+  </si>
+  <si>
+    <t>一键将客户订单转为销售订单（带审批）</t>
+  </si>
+  <si>
+    <t>销售订单</t>
+  </si>
+  <si>
+    <t>内部执行单；基于客户订单生成，用于排产、发货、开票等内部流程，支持折扣、赠品、分批发货设置。可进行信用检查。</t>
+  </si>
+  <si>
+    <t>发货管理</t>
+  </si>
+  <si>
+    <t>根据订单生成发货单，通知仓库备货。支持部分发货</t>
+  </si>
+  <si>
+    <t>销售出库</t>
+  </si>
+  <si>
+    <t>仓库完成出库操作，更新库存，生成出库单。</t>
+  </si>
+  <si>
+    <t>销售退货</t>
+  </si>
+  <si>
+    <t>客户退货登记，质检后决定返修、换货或报废。</t>
   </si>
   <si>
     <t>PA收发清单</t>
   </si>
   <si>
+    <t>针对项目型订单的配套发料管理，确保按项目配套出库，避免错发漏发</t>
+  </si>
+  <si>
     <t>采购管理</t>
   </si>
   <si>
-    <t>采购申请单</t>
+    <t>采购申请</t>
+  </si>
+  <si>
+    <t>各部门提交采购需求（物料、设备工具、数量、需求日期），支持多级审批流（按金额分级）。可关联项目或生产任务。</t>
   </si>
   <si>
     <t>采购计划</t>
   </si>
   <si>
-    <t>成品入库</t>
-  </si>
-  <si>
-    <t>半成品入库</t>
-  </si>
-  <si>
-    <t>原材料采购</t>
-  </si>
-  <si>
-    <t>辅材采购</t>
-  </si>
-  <si>
-    <t>标准件采购</t>
-  </si>
-  <si>
-    <t>工具库采购</t>
-  </si>
-  <si>
-    <t>工装备件采购</t>
+    <t>汇总多个采购申请，进行合并采购，优化采购批次与成本。支持MRP运算后自动生成采购建议。</t>
+  </si>
+  <si>
+    <t>采购订单</t>
+  </si>
+  <si>
+    <t>向供应商正式下单，包含物料、数量、单价、交货日期、付款条款等。支持订单变更（增减量、延期）。</t>
+  </si>
+  <si>
+    <t>到货管理</t>
+  </si>
+  <si>
+    <t>供应商送货后登记到货单，生成待检任务，通知质检部门。支持部分到货。</t>
+  </si>
+  <si>
+    <t>采购入库</t>
+  </si>
+  <si>
+    <t>质检合格后办理入库，更新库存，生成入库单。支持按订单分批入库。</t>
+  </si>
+  <si>
+    <t>采购退货</t>
+  </si>
+  <si>
+    <t>对不合格物料办理退货，生成退货单，扣减库存，更新供应商绩效</t>
   </si>
   <si>
     <t>库房管理</t>
   </si>
   <si>
-    <t>废品单管理</t>
-  </si>
-  <si>
-    <t>返修品管理</t>
-  </si>
-  <si>
-    <t>返修品入库</t>
-  </si>
-  <si>
-    <t>返修品出库</t>
-  </si>
-  <si>
-    <t>成品库</t>
-  </si>
-  <si>
-    <t>半成品库</t>
-  </si>
-  <si>
-    <t>原材料库</t>
-  </si>
-  <si>
-    <t>辅助材料库</t>
-  </si>
-  <si>
-    <t>标准件库</t>
-  </si>
-  <si>
-    <t>工具库</t>
-  </si>
-  <si>
-    <t>工装备件库</t>
+    <t>入库管理</t>
+  </si>
+  <si>
+    <t>支持采购入库、生产入库、委外回货、退货入库等类型。支持扫码入库，自动更新库存</t>
+  </si>
+  <si>
+    <t>出库管理</t>
+  </si>
+  <si>
+    <t>支持销售出库、生产领料、调拨出库、样品出库等。支持先进先出（FIFO）控制。</t>
+  </si>
+  <si>
+    <t>库存盘点</t>
+  </si>
+  <si>
+    <t>支持周期盘点、动态盘点、全盘。PDA扫码比对账面与实存，生成盘点差异报告</t>
+  </si>
+  <si>
+    <t>库存调拨</t>
+  </si>
+  <si>
+    <t>不同仓库或库位之间的物料转移，生成调拨单，支持审批。</t>
+  </si>
+  <si>
+    <t>批次/序列号管理</t>
+  </si>
+  <si>
+    <t>对关键物料启用批次或序列号追踪，实现正向与反向追溯（如质量问题召回）。</t>
+  </si>
+  <si>
+    <t>废品与返修管理</t>
+  </si>
+  <si>
+    <t>登记废品数量与原因；返修品入库后可触发维修任务，修复后重新入库或报废。</t>
+  </si>
+  <si>
+    <t>设备管理</t>
+  </si>
+  <si>
+    <t>工业设备</t>
+  </si>
+  <si>
+    <t>设备类型设置</t>
+  </si>
+  <si>
+    <t>设置设备类型，如数控车床、粉碎机等</t>
+  </si>
+  <si>
+    <t>设备台账</t>
+  </si>
+  <si>
+    <t>查看每台设备使用状态、所属车间、点检记录、保养记录、维修记录，新增时自动生成二维码</t>
+  </si>
+  <si>
+    <t>设备报废</t>
+  </si>
+  <si>
+    <t>可对设备进行报废申请，多级审批人审核通过后，设备报废完成并从设备台账更新设备状态</t>
+  </si>
+  <si>
+    <t>点检与保养</t>
+  </si>
+  <si>
+    <t>点检保养项目</t>
+  </si>
+  <si>
+    <t>设置设备是点检或者保养，项目的内容</t>
+  </si>
+  <si>
+    <t>点检保养计划</t>
+  </si>
+  <si>
+    <t>设置设备保养或点检计划，添加设备信息与人员。默认保存时为草稿，添加设备信息后可执行。执行后生成点检或保养记录</t>
+  </si>
+  <si>
+    <t>点检记录</t>
+  </si>
+  <si>
+    <t>查询执行中或已完成的记录，可取消执行中的点检计划</t>
+  </si>
+  <si>
+    <t>保养记录</t>
+  </si>
+  <si>
+    <t>查询执行中或已完成的记录，可取消执行中的保养计划</t>
+  </si>
+  <si>
+    <t>设备维修</t>
+  </si>
+  <si>
+    <t>维修单</t>
+  </si>
+  <si>
+    <t>对需要维修的设备发起维修单并制定维修人员，审核通过后进行维修。</t>
+  </si>
+  <si>
+    <t>维修记录</t>
+  </si>
+  <si>
+    <t>已完成的设备维修记录</t>
+  </si>
+  <si>
+    <t>工艺装备</t>
+  </si>
+  <si>
+    <t>类型设置</t>
+  </si>
+  <si>
+    <t>设置装备类型，如夹具、模具等</t>
+  </si>
+  <si>
+    <t>装备台账</t>
+  </si>
+  <si>
+    <t>查看每台装备使用状态、所属车间、点检记录、保养记录、维修记录，新增时自动生成二维码</t>
+  </si>
+  <si>
+    <t>装备报废</t>
+  </si>
+  <si>
+    <t>可对装备进行报废申请，多级审批人审核通过后，设备报废完成并从设备台账更新设备状态</t>
   </si>
   <si>
     <t>综合查询</t>
@@ -182,6 +410,36 @@
     <t>生产查询</t>
   </si>
   <si>
+    <t>查询订单生产进度、工序状态</t>
+  </si>
+  <si>
+    <t>物料消耗查询</t>
+  </si>
+  <si>
+    <t>查询某订单/产品的物料使用情况</t>
+  </si>
+  <si>
+    <t>库存流水</t>
+  </si>
+  <si>
+    <t>查看某物料的出入库明细</t>
+  </si>
+  <si>
+    <t>排班管理</t>
+  </si>
+  <si>
+    <t>班组设置</t>
+  </si>
+  <si>
+    <t>排班计划</t>
+  </si>
+  <si>
+    <t>节假日设置</t>
+  </si>
+  <si>
+    <t>排版日历</t>
+  </si>
+  <si>
     <t>系统管理</t>
   </si>
   <si>
@@ -224,19 +482,37 @@
     <t>消息通知</t>
   </si>
   <si>
+    <t>推送审批、任务、预警等消息</t>
+  </si>
+  <si>
     <t>首页</t>
   </si>
   <si>
+    <t>显示待办、KPI、快捷入口</t>
+  </si>
+  <si>
     <t>生产</t>
   </si>
   <si>
+    <t>手机端扫码报工、工序确认</t>
+  </si>
+  <si>
     <t>设备</t>
   </si>
   <si>
+    <t>手机端提交设备故障</t>
+  </si>
+  <si>
     <t>仓储</t>
   </si>
   <si>
-    <t>质量</t>
+    <t>入库扫码 | 扫码完成入库操作，出库扫码 | 扫码出库，自动扣减库存</t>
+  </si>
+  <si>
+    <t>我的</t>
+  </si>
+  <si>
+    <t>个人登录、退出等</t>
   </si>
 </sst>
 </file>
@@ -249,7 +525,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +550,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF111133"/>
+      <name val="helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -420,6 +702,12 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF111133"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -621,7 +909,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -642,6 +930,43 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -760,138 +1085,140 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -902,14 +1229,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1261,558 +1594,860 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <dimension ref="A1:E74"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7545454545455" customWidth="1"/>
-    <col min="2" max="2" width="22.1272727272727" customWidth="1"/>
-    <col min="3" max="3" width="27.3727272727273" customWidth="1"/>
-    <col min="4" max="4" width="31.2545454545455" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="1" max="1" width="13.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1296296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3703703703704" style="1" customWidth="1"/>
+    <col min="4" max="4" width="126.814814814815" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.4537037037037" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="16.2" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="15.6" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" ht="15.6" spans="1:5">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" ht="16.5" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:5">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" ht="15.6" spans="1:5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" ht="15.6" spans="1:5">
+      <c r="A6" s="4"/>
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" ht="15.6" spans="1:5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="9"/>
+    </row>
+    <row r="8" ht="15.6" spans="1:5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" ht="15.6" spans="1:5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" ht="16.5" spans="1:5">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
+    <row r="11" ht="15.6" spans="1:5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" ht="16.5" spans="1:5">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="3"/>
+    <row r="12" ht="15.6" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" ht="16.5" spans="1:5">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
+    <row r="14" ht="15.6" spans="1:5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" ht="15.6" spans="1:5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" ht="15.6" spans="1:5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" ht="15.6" spans="1:5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" ht="15.6" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" ht="15.6" spans="1:5">
+      <c r="A21" s="11"/>
+      <c r="B21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
+    <row r="22" ht="15.6" spans="1:5">
+      <c r="A22" s="11"/>
+      <c r="B22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="3"/>
+    <row r="23" ht="15.6" spans="1:5">
+      <c r="A23" s="11"/>
+      <c r="B23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
+    <row r="24" ht="15.6" spans="1:5">
+      <c r="A24" s="11"/>
+      <c r="B24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
+    <row r="25" ht="15.6" spans="1:5">
+      <c r="A25" s="11"/>
+      <c r="B25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
+    <row r="26" ht="15.6" spans="1:5">
+      <c r="A26" s="8"/>
+      <c r="B26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" ht="16.5" spans="1:5">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A30" s="2"/>
-      <c r="B30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A31" s="2"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="6"/>
+    <row r="27" ht="15.6" spans="1:5">
+      <c r="A27" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" ht="15.6" spans="1:5">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29" ht="15.6" spans="1:5">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" ht="15.6" spans="1:5">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" ht="15.6" spans="1:5">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" ht="15.6" spans="1:5">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="10"/>
+    </row>
+    <row r="33" ht="15.6" spans="1:5">
+      <c r="A33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="6"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="6"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="6"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="6"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" ht="16.5" spans="1:5">
-      <c r="A40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" ht="16.5" spans="1:5">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" ht="16.5" spans="1:5">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="43" ht="16.5" spans="1:5">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" ht="16.5" spans="1:5">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" ht="16.5" spans="1:5">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="6"/>
-    </row>
-    <row r="46" ht="16.5" spans="1:5">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" ht="16.5" spans="1:5">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" ht="16.5" spans="1:5">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" ht="16.5" spans="1:5">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" ht="16.5" spans="1:5">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A51" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" ht="16.5" spans="1:5">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" ht="16.5" spans="1:5">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" ht="16.5" spans="1:5">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="6"/>
-    </row>
-    <row r="55" ht="16.5" spans="1:5">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="6"/>
-    </row>
-    <row r="56" ht="16.5" spans="1:5">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="6"/>
+      <c r="A39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A40" s="4"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="10"/>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A41" s="4"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A42" s="4"/>
+      <c r="B42" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E42" s="10"/>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A43" s="4"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A44" s="4"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A45" s="4"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A46" s="4"/>
+      <c r="B46" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="10"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A47" s="4"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="10"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A48" s="4"/>
+      <c r="B48" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" s="10"/>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A49" s="4"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" s="10"/>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A50" s="4"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" s="10"/>
+    </row>
+    <row r="51" ht="16.5" customHeight="1" spans="1:5">
+      <c r="A51" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="10"/>
+    </row>
+    <row r="52" ht="15.6" spans="1:5">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="10"/>
+    </row>
+    <row r="53" ht="15.6" spans="1:5">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" s="10"/>
+    </row>
+    <row r="54" ht="15.6" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="10"/>
+    </row>
+    <row r="55" ht="15.6" spans="1:5">
+      <c r="A55" s="11"/>
+      <c r="B55" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="10"/>
+    </row>
+    <row r="56" ht="15.6" spans="1:5">
+      <c r="A56" s="11"/>
+      <c r="B56" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="10"/>
+    </row>
+    <row r="57" ht="15.6" spans="1:5">
+      <c r="A57" s="8"/>
+      <c r="B57" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="10"/>
+    </row>
+    <row r="58" ht="15.6" spans="1:5">
+      <c r="A58" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="10"/>
+    </row>
+    <row r="59" ht="15.6" spans="1:5">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="10"/>
+    </row>
+    <row r="60" ht="15.6" spans="1:5">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="10"/>
+    </row>
+    <row r="61" ht="15.6" spans="1:5">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="10"/>
+    </row>
+    <row r="62" ht="15.6" spans="1:5">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="10"/>
+    </row>
+    <row r="63" ht="15.6" spans="1:5">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="10"/>
+    </row>
+    <row r="64" ht="15.6" spans="1:5">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="10"/>
+    </row>
+    <row r="65" ht="15.6" spans="1:5">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="10"/>
+    </row>
+    <row r="66" ht="15.6" spans="1:5">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="10"/>
+    </row>
+    <row r="67" ht="15.6" spans="1:5">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="10"/>
+    </row>
+    <row r="68" ht="15.6" spans="1:5">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="10"/>
+    </row>
+    <row r="69" ht="13.5" customHeight="1" spans="1:5">
+      <c r="A69" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="13"/>
+      <c r="D69" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E69" s="10"/>
+    </row>
+    <row r="70" ht="15.6" spans="1:5">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="13"/>
+      <c r="D70" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E70" s="10"/>
+    </row>
+    <row r="71" ht="15.6" spans="1:5">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="13"/>
+      <c r="D71" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" s="10"/>
+    </row>
+    <row r="72" ht="15.6" spans="1:5">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" s="13"/>
+      <c r="D72" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E72" s="10"/>
+    </row>
+    <row r="73" ht="15.6" spans="1:5">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" s="13"/>
+      <c r="D73" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E73" s="10"/>
+    </row>
+    <row r="74" ht="15.6" spans="1:5">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C74" s="13"/>
+      <c r="D74" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E74" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A28"/>
-    <mergeCell ref="A29:A38"/>
-    <mergeCell ref="A40:A50"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="B30:B31"/>
+  <mergeCells count="17">
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A39:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A68"/>
+    <mergeCell ref="A69:A74"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B48:B50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView windowWidth="24750" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
@@ -1595,17 +1595,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1296296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3703703703704" style="1" customWidth="1"/>
-    <col min="4" max="4" width="126.814814814815" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.4537037037037" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7545454545455" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1272727272727" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="126.818181818182" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.4545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" spans="1:5">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:5">
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" ht="15.6" spans="1:5">
+    <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" ht="15.6" spans="1:5">
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>11</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" ht="15.6" spans="1:5">
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" ht="15.6" spans="1:5">
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4"/>
       <c r="B6" s="7" t="s">
         <v>16</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" ht="15.6" spans="1:5">
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="4"/>
       <c r="B7" s="8"/>
       <c r="C7" s="4" t="s">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" ht="15.6" spans="1:5">
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>21</v>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="15.6" spans="1:5">
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>23</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" ht="15.6" spans="1:5">
+    <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>25</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" ht="15.6" spans="1:5">
+    <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>27</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" ht="15.6" spans="1:5">
+    <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" ht="15.6" spans="1:5">
+    <row r="13" ht="16.5" spans="1:5">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" ht="15.6" spans="1:5">
+    <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>34</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" ht="15.6" spans="1:5">
+    <row r="15" ht="16.5" spans="1:5">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>36</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" ht="15.6" spans="1:5">
+    <row r="16" ht="16.5" spans="1:5">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>38</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" ht="15.6" spans="1:5">
+    <row r="17" ht="16.5" spans="1:5">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>40</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="E17" s="10"/>
     </row>
-    <row r="18" ht="15.6" spans="1:5">
+    <row r="18" ht="16.5" spans="1:5">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>42</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E18" s="10"/>
     </row>
-    <row r="19" ht="15.6" spans="1:5">
+    <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>44</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" ht="15.6" spans="1:5">
+    <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="7" t="s">
         <v>46</v>
       </c>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="15.6" spans="1:5">
+    <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="11"/>
       <c r="B21" s="4" t="s">
         <v>49</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" ht="15.6" spans="1:5">
+    <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="11"/>
       <c r="B22" s="4" t="s">
         <v>51</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" ht="15.6" spans="1:5">
+    <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="11"/>
       <c r="B23" s="4" t="s">
         <v>53</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" ht="15.6" spans="1:5">
+    <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="11"/>
       <c r="B24" s="4" t="s">
         <v>55</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" ht="15.6" spans="1:5">
+    <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="11"/>
       <c r="B25" s="4" t="s">
         <v>57</v>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" ht="15.6" spans="1:5">
+    <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="8"/>
       <c r="B26" s="4" t="s">
         <v>59</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" ht="15.6" spans="1:5">
+    <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E27" s="10"/>
     </row>
-    <row r="28" ht="15.6" spans="1:5">
+    <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>64</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="E28" s="10"/>
     </row>
-    <row r="29" ht="15.6" spans="1:5">
+    <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>66</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E29" s="10"/>
     </row>
-    <row r="30" ht="15.6" spans="1:5">
+    <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>68</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E30" s="10"/>
     </row>
-    <row r="31" ht="15.6" spans="1:5">
+    <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>70</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="E31" s="10"/>
     </row>
-    <row r="32" ht="15.6" spans="1:5">
+    <row r="32" ht="16.5" spans="1:5">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>72</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="E32" s="10"/>
     </row>
-    <row r="33" ht="15.6" spans="1:5">
+    <row r="33" ht="16.5" spans="1:5">
       <c r="A33" s="4" t="s">
         <v>74</v>
       </c>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E51" s="10"/>
     </row>
-    <row r="52" ht="15.6" spans="1:5">
+    <row r="52" ht="16.5" spans="1:5">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>119</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="E52" s="10"/>
     </row>
-    <row r="53" ht="15.6" spans="1:5">
+    <row r="53" ht="16.5" spans="1:5">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>121</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E53" s="10"/>
     </row>
-    <row r="54" ht="15.6" spans="1:5">
+    <row r="54" ht="16.5" spans="1:5">
       <c r="A54" s="7" t="s">
         <v>123</v>
       </c>
@@ -2233,7 +2233,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="10"/>
     </row>
-    <row r="55" ht="15.6" spans="1:5">
+    <row r="55" ht="16.5" spans="1:5">
       <c r="A55" s="11"/>
       <c r="B55" s="4" t="s">
         <v>125</v>
@@ -2242,7 +2242,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="10"/>
     </row>
-    <row r="56" ht="15.6" spans="1:5">
+    <row r="56" ht="16.5" spans="1:5">
       <c r="A56" s="11"/>
       <c r="B56" s="4" t="s">
         <v>126</v>
@@ -2251,7 +2251,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="10"/>
     </row>
-    <row r="57" ht="15.6" spans="1:5">
+    <row r="57" ht="16.5" spans="1:5">
       <c r="A57" s="8"/>
       <c r="B57" s="4" t="s">
         <v>127</v>
@@ -2260,7 +2260,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="10"/>
     </row>
-    <row r="58" ht="15.6" spans="1:5">
+    <row r="58" ht="16.5" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>128</v>
       </c>
@@ -2271,7 +2271,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="10"/>
     </row>
-    <row r="59" ht="15.6" spans="1:5">
+    <row r="59" ht="16.5" spans="1:5">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>130</v>
@@ -2280,7 +2280,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="10"/>
     </row>
-    <row r="60" ht="15.6" spans="1:5">
+    <row r="60" ht="16.5" spans="1:5">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>131</v>
@@ -2289,7 +2289,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="10"/>
     </row>
-    <row r="61" ht="15.6" spans="1:5">
+    <row r="61" ht="16.5" spans="1:5">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>132</v>
@@ -2298,7 +2298,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="10"/>
     </row>
-    <row r="62" ht="15.6" spans="1:5">
+    <row r="62" ht="16.5" spans="1:5">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>133</v>
@@ -2307,7 +2307,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="10"/>
     </row>
-    <row r="63" ht="15.6" spans="1:5">
+    <row r="63" ht="16.5" spans="1:5">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>134</v>
@@ -2316,7 +2316,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="10"/>
     </row>
-    <row r="64" ht="15.6" spans="1:5">
+    <row r="64" ht="16.5" spans="1:5">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>135</v>
@@ -2325,7 +2325,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="10"/>
     </row>
-    <row r="65" ht="15.6" spans="1:5">
+    <row r="65" ht="16.5" spans="1:5">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>136</v>
@@ -2334,7 +2334,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="10"/>
     </row>
-    <row r="66" ht="15.6" spans="1:5">
+    <row r="66" ht="16.5" spans="1:5">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>137</v>
@@ -2343,7 +2343,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="10"/>
     </row>
-    <row r="67" ht="15.6" spans="1:5">
+    <row r="67" ht="16.5" spans="1:5">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>138</v>
@@ -2352,7 +2352,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="10"/>
     </row>
-    <row r="68" ht="15.6" spans="1:5">
+    <row r="68" ht="16.5" spans="1:5">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>139</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E69" s="10"/>
     </row>
-    <row r="70" ht="15.6" spans="1:5">
+    <row r="70" ht="16.5" spans="1:5">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>143</v>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="E70" s="10"/>
     </row>
-    <row r="71" ht="15.6" spans="1:5">
+    <row r="71" ht="16.5" spans="1:5">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>145</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E71" s="10"/>
     </row>
-    <row r="72" ht="15.6" spans="1:5">
+    <row r="72" ht="16.5" spans="1:5">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>147</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E72" s="10"/>
     </row>
-    <row r="73" ht="15.6" spans="1:5">
+    <row r="73" ht="16.5" spans="1:5">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>149</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="E73" s="10"/>
     </row>
-    <row r="74" ht="15.6" spans="1:5">
+    <row r="74" ht="16.5" spans="1:5">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>151</v>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12200"/>
+    <workbookView windowWidth="24750" windowHeight="12200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
+    <sheet name="一阶段" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="142">
   <si>
     <t>一级菜单</t>
   </si>
@@ -476,43 +477,10 @@
     <t>编码生成规则</t>
   </si>
   <si>
-    <t>手机端</t>
-  </si>
-  <si>
-    <t>消息通知</t>
-  </si>
-  <si>
-    <t>推送审批、任务、预警等消息</t>
-  </si>
-  <si>
-    <t>首页</t>
-  </si>
-  <si>
-    <t>显示待办、KPI、快捷入口</t>
-  </si>
-  <si>
-    <t>生产</t>
-  </si>
-  <si>
-    <t>手机端扫码报工、工序确认</t>
-  </si>
-  <si>
-    <t>设备</t>
-  </si>
-  <si>
-    <t>手机端提交设备故障</t>
-  </si>
-  <si>
-    <t>仓储</t>
-  </si>
-  <si>
-    <t>入库扫码 | 扫码完成入库操作，出库扫码 | 扫码出库，自动扣减库存</t>
-  </si>
-  <si>
-    <t>我的</t>
-  </si>
-  <si>
-    <t>个人登录、退出等</t>
+    <t>√</t>
+  </si>
+  <si>
+    <t>生产领料</t>
   </si>
 </sst>
 </file>
@@ -953,9 +921,7 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -966,7 +932,9 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1215,16 +1183,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1232,20 +1210,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1594,843 +1568,775 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7545454545455" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1272727272727" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="126.818181818182" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.4545454545455" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
+    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" ht="16.5" spans="1:5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="13"/>
     </row>
     <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" ht="16.5" spans="1:5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" ht="16.5" spans="1:5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" ht="16.5" spans="1:5">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" ht="16.5" spans="1:5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" ht="16.5" spans="1:5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" ht="16.5" spans="1:5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="10"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" ht="16.5" spans="1:5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="10"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" ht="16.5" spans="1:5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="10"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="10"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="10"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="11"/>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="11"/>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="14"/>
+      <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="2"/>
+      <c r="D22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="6"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="11"/>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="2"/>
+      <c r="D23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="11"/>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="6"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="11"/>
-      <c r="B25" s="4" t="s">
+      <c r="A25" s="14"/>
+      <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="6"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="8"/>
-      <c r="B26" s="4" t="s">
+      <c r="A26" s="12"/>
+      <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="6"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" ht="16.5" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="10"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="10"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4" t="s">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5" t="s">
+      <c r="C29" s="2"/>
+      <c r="D29" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="10"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4" t="s">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="2"/>
+      <c r="D30" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E30" s="10"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4" t="s">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="12" t="s">
+      <c r="C31" s="2"/>
+      <c r="D31" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="10"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4" t="s">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="2"/>
+      <c r="D32" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="10"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="2"/>
+      <c r="D33" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="10"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4" t="s">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="2"/>
+      <c r="D34" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="10"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4" t="s">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="12" t="s">
+      <c r="C35" s="2"/>
+      <c r="D35" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="10"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4" t="s">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="12" t="s">
+      <c r="C36" s="2"/>
+      <c r="D36" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="10"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4" t="s">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="12" t="s">
+      <c r="C37" s="2"/>
+      <c r="D37" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="10"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4" t="s">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="12" t="s">
+      <c r="C38" s="2"/>
+      <c r="D38" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E38" s="10"/>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="10"/>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A40" s="4"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="4" t="s">
+      <c r="A40" s="2"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="10"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A41" s="4"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="4" t="s">
+      <c r="A41" s="2"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E41" s="10"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A42" s="4"/>
-      <c r="B42" s="7" t="s">
+      <c r="A42" s="2"/>
+      <c r="B42" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E42" s="10"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A43" s="4"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="4" t="s">
+      <c r="A43" s="2"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="10"/>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A44" s="4"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="4" t="s">
+      <c r="A44" s="2"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="10"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A45" s="4"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="4" t="s">
+      <c r="A45" s="2"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="10"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A46" s="4"/>
-      <c r="B46" s="7" t="s">
+      <c r="A46" s="2"/>
+      <c r="B46" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E46" s="10"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A47" s="4"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="4" t="s">
+      <c r="A47" s="2"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E47" s="10"/>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A48" s="4"/>
-      <c r="B48" s="7" t="s">
+      <c r="A48" s="2"/>
+      <c r="B48" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="10"/>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A49" s="4"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="4" t="s">
+      <c r="A49" s="2"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E49" s="10"/>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A50" s="4"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="4" t="s">
+      <c r="A50" s="2"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E50" s="10"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5" t="s">
+      <c r="C51" s="2"/>
+      <c r="D51" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E51" s="10"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" ht="16.5" spans="1:5">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4" t="s">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5" t="s">
+      <c r="C52" s="9"/>
+      <c r="D52" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E52" s="10"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" ht="16.5" spans="1:5">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4" t="s">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5" t="s">
+      <c r="C53" s="9"/>
+      <c r="D53" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E53" s="10"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" ht="16.5" spans="1:5">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="10"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" ht="16.5" spans="1:5">
-      <c r="A55" s="11"/>
-      <c r="B55" s="4" t="s">
+      <c r="A55" s="14"/>
+      <c r="B55" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="10"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="3"/>
     </row>
     <row r="56" ht="16.5" spans="1:5">
-      <c r="A56" s="11"/>
-      <c r="B56" s="4" t="s">
+      <c r="A56" s="14"/>
+      <c r="B56" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="10"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" ht="16.5" spans="1:5">
-      <c r="A57" s="8"/>
-      <c r="B57" s="4" t="s">
+      <c r="A57" s="12"/>
+      <c r="B57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="10"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" ht="16.5" spans="1:5">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="10"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" ht="16.5" spans="1:5">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4" t="s">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="10"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4" t="s">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="10"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" ht="16.5" spans="1:5">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4" t="s">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="10"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" ht="16.5" spans="1:5">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4" t="s">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="10"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="3"/>
     </row>
     <row r="63" ht="16.5" spans="1:5">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4" t="s">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="10"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" ht="16.5" spans="1:5">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4" t="s">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="10"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" ht="16.5" spans="1:5">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4" t="s">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="10"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" ht="16.5" spans="1:5">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4" t="s">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="10"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" ht="16.5" spans="1:5">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4" t="s">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="10"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" ht="16.5" spans="1:5">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4" t="s">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="10"/>
-    </row>
-    <row r="69" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A69" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C69" s="13"/>
-      <c r="D69" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E69" s="10"/>
-    </row>
-    <row r="70" ht="16.5" spans="1:5">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C70" s="13"/>
-      <c r="D70" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E70" s="10"/>
-    </row>
-    <row r="71" ht="16.5" spans="1:5">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C71" s="13"/>
-      <c r="D71" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E71" s="10"/>
-    </row>
-    <row r="72" ht="16.5" spans="1:5">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E72" s="10"/>
-    </row>
-    <row r="73" ht="16.5" spans="1:5">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C73" s="13"/>
-      <c r="D73" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E73" s="10"/>
-    </row>
-    <row r="74" ht="16.5" spans="1:5">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E74" s="10"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="A2:A11"/>
     <mergeCell ref="A12:A19"/>
     <mergeCell ref="A20:A26"/>
@@ -2440,7 +2346,6 @@
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="A58:A68"/>
-    <mergeCell ref="A69:A74"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
@@ -2453,4 +2358,158 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="16.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="16.5454545454545" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:4">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:4">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:4">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:4">
+      <c r="A10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:4">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="6"/>
+      <c r="B13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B4:B5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12200" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="142">
   <si>
     <t>一级菜单</t>
   </si>
@@ -1183,7 +1183,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1207,17 +1207,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -1569,17 +1560,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
-    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
+    <col min="1" max="1" width="13.75" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.1296296296296" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.3703703703704" style="7" customWidth="1"/>
+    <col min="4" max="4" width="126.814814814815" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.4537037037037" style="7" customWidth="1"/>
     <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
+    <row r="1" ht="16.2" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:5">
+    <row r="2" ht="15.6" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1611,7 +1602,7 @@
       </c>
       <c r="E2" s="10"/>
     </row>
-    <row r="3" ht="16.5" spans="1:5">
+    <row r="3" ht="15.6" spans="1:5">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
@@ -1622,7 +1613,7 @@
       </c>
       <c r="E3" s="10"/>
     </row>
-    <row r="4" ht="16.5" spans="1:5">
+    <row r="4" ht="15.6" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -1635,7 +1626,7 @@
       </c>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" ht="16.5" spans="1:5">
+    <row r="5" ht="15.6" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
@@ -1646,9 +1637,9 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" ht="16.5" spans="1:5">
+    <row r="6" ht="15.6" spans="1:5">
       <c r="A6" s="2"/>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1659,18 +1650,18 @@
       </c>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" ht="16.5" spans="1:5">
+    <row r="7" ht="15.6" spans="1:5">
       <c r="A7" s="2"/>
-      <c r="B7" s="12"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" ht="15.6" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>21</v>
@@ -1679,9 +1670,9 @@
       <c r="D8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" ht="15.6" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>23</v>
@@ -1692,7 +1683,7 @@
       </c>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" ht="16.5" spans="1:5">
+    <row r="10" ht="15.6" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>25</v>
@@ -1703,7 +1694,7 @@
       </c>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" ht="16.5" spans="1:5">
+    <row r="11" ht="15.6" spans="1:5">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -1714,7 +1705,7 @@
       </c>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" ht="16.5" spans="1:5">
+    <row r="12" ht="15.6" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1727,7 +1718,7 @@
       </c>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" ht="16.5" spans="1:5">
+    <row r="13" ht="15.6" spans="1:5">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>32</v>
@@ -1738,7 +1729,7 @@
       </c>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" ht="16.5" spans="1:5">
+    <row r="14" ht="15.6" spans="1:5">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>34</v>
@@ -1749,7 +1740,7 @@
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" ht="16.5" spans="1:5">
+    <row r="15" ht="15.6" spans="1:5">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>36</v>
@@ -1760,7 +1751,7 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" ht="16.5" spans="1:5">
+    <row r="16" ht="15.6" spans="1:5">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>38</v>
@@ -1771,7 +1762,7 @@
       </c>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" ht="16.5" spans="1:5">
+    <row r="17" ht="15.6" spans="1:5">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>40</v>
@@ -1782,7 +1773,7 @@
       </c>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" ht="16.5" spans="1:5">
+    <row r="18" ht="15.6" spans="1:5">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>42</v>
@@ -1793,7 +1784,7 @@
       </c>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" ht="16.5" spans="1:5">
+    <row r="19" ht="15.6" spans="1:5">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>44</v>
@@ -1804,8 +1795,8 @@
       </c>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="11" t="s">
+    <row r="20" ht="15.6" spans="1:5">
+      <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1817,8 +1808,8 @@
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="14"/>
+    <row r="21" ht="15.6" spans="1:5">
+      <c r="A21" s="5"/>
       <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
@@ -1828,8 +1819,8 @@
       </c>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="14"/>
+    <row r="22" ht="15.6" spans="1:5">
+      <c r="A22" s="5"/>
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
@@ -1839,8 +1830,8 @@
       </c>
       <c r="E22" s="10"/>
     </row>
-    <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="14"/>
+    <row r="23" ht="15.6" spans="1:5">
+      <c r="A23" s="5"/>
       <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
@@ -1850,8 +1841,8 @@
       </c>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="14"/>
+    <row r="24" ht="15.6" spans="1:5">
+      <c r="A24" s="5"/>
       <c r="B24" s="2" t="s">
         <v>55</v>
       </c>
@@ -1861,8 +1852,8 @@
       </c>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="14"/>
+    <row r="25" ht="15.6" spans="1:5">
+      <c r="A25" s="5"/>
       <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
@@ -1872,8 +1863,8 @@
       </c>
       <c r="E25" s="10"/>
     </row>
-    <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="12"/>
+    <row r="26" ht="15.6" spans="1:5">
+      <c r="A26" s="6"/>
       <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
@@ -1883,7 +1874,7 @@
       </c>
       <c r="E26" s="10"/>
     </row>
-    <row r="27" ht="16.5" spans="1:5">
+    <row r="27" ht="15.6" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -1896,7 +1887,7 @@
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" ht="16.5" spans="1:5">
+    <row r="28" ht="15.6" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>64</v>
@@ -1907,7 +1898,7 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" ht="16.5" spans="1:5">
+    <row r="29" ht="15.6" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>66</v>
@@ -1918,7 +1909,7 @@
       </c>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" ht="16.5" spans="1:5">
+    <row r="30" ht="15.6" spans="1:5">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>68</v>
@@ -1929,29 +1920,29 @@
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" ht="16.5" spans="1:5">
+    <row r="31" ht="15.6" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="12" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" ht="16.5" spans="1:5">
+    <row r="32" ht="15.6" spans="1:5">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" ht="16.5" spans="1:5">
+    <row r="33" ht="15.6" spans="1:5">
       <c r="A33" s="2" t="s">
         <v>74</v>
       </c>
@@ -1959,7 +1950,7 @@
         <v>75</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="12" t="s">
         <v>76</v>
       </c>
       <c r="E33" s="3"/>
@@ -1970,7 +1961,7 @@
         <v>77</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="12" t="s">
         <v>78</v>
       </c>
       <c r="E34" s="3"/>
@@ -1981,7 +1972,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="12" t="s">
         <v>80</v>
       </c>
       <c r="E35" s="3"/>
@@ -1992,7 +1983,7 @@
         <v>81</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E36" s="3"/>
@@ -2003,7 +1994,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="12" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="3"/>
@@ -2014,7 +2005,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E38" s="3"/>
@@ -2023,7 +2014,7 @@
       <c r="A39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2036,7 +2027,7 @@
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:5">
       <c r="A40" s="2"/>
-      <c r="B40" s="14"/>
+      <c r="B40" s="5"/>
       <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
@@ -2047,7 +2038,7 @@
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:5">
       <c r="A41" s="2"/>
-      <c r="B41" s="12"/>
+      <c r="B41" s="6"/>
       <c r="C41" s="2" t="s">
         <v>93</v>
       </c>
@@ -2058,7 +2049,7 @@
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:5">
       <c r="A42" s="2"/>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2071,7 +2062,7 @@
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:5">
       <c r="A43" s="2"/>
-      <c r="B43" s="14"/>
+      <c r="B43" s="5"/>
       <c r="C43" s="2" t="s">
         <v>98</v>
       </c>
@@ -2082,7 +2073,7 @@
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:5">
       <c r="A44" s="2"/>
-      <c r="B44" s="14"/>
+      <c r="B44" s="5"/>
       <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
@@ -2093,7 +2084,7 @@
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:5">
       <c r="A45" s="2"/>
-      <c r="B45" s="12"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="2" t="s">
         <v>102</v>
       </c>
@@ -2104,7 +2095,7 @@
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:5">
       <c r="A46" s="2"/>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="4" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -2117,7 +2108,7 @@
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:5">
       <c r="A47" s="2"/>
-      <c r="B47" s="12"/>
+      <c r="B47" s="6"/>
       <c r="C47" s="2" t="s">
         <v>107</v>
       </c>
@@ -2128,7 +2119,7 @@
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:5">
       <c r="A48" s="2"/>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -2141,7 +2132,7 @@
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:5">
       <c r="A49" s="2"/>
-      <c r="B49" s="14"/>
+      <c r="B49" s="5"/>
       <c r="C49" s="2" t="s">
         <v>112</v>
       </c>
@@ -2152,7 +2143,7 @@
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:5">
       <c r="A50" s="2"/>
-      <c r="B50" s="12"/>
+      <c r="B50" s="6"/>
       <c r="C50" s="2" t="s">
         <v>114</v>
       </c>
@@ -2174,7 +2165,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" ht="16.5" spans="1:5">
+    <row r="52" ht="15.6" spans="1:5">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>119</v>
@@ -2185,7 +2176,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" ht="16.5" spans="1:5">
+    <row r="53" ht="15.6" spans="1:5">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>121</v>
@@ -2196,8 +2187,8 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" ht="16.5" spans="1:5">
-      <c r="A54" s="11" t="s">
+    <row r="54" ht="15.6" spans="1:5">
+      <c r="A54" s="4" t="s">
         <v>123</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2207,8 +2198,8 @@
       <c r="D54" s="9"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" ht="16.5" spans="1:5">
-      <c r="A55" s="14"/>
+    <row r="55" ht="15.6" spans="1:5">
+      <c r="A55" s="5"/>
       <c r="B55" s="2" t="s">
         <v>125</v>
       </c>
@@ -2216,8 +2207,8 @@
       <c r="D55" s="9"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" ht="16.5" spans="1:5">
-      <c r="A56" s="14"/>
+    <row r="56" ht="15.6" spans="1:5">
+      <c r="A56" s="5"/>
       <c r="B56" s="2" t="s">
         <v>126</v>
       </c>
@@ -2225,8 +2216,8 @@
       <c r="D56" s="9"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" ht="16.5" spans="1:5">
-      <c r="A57" s="12"/>
+    <row r="57" ht="15.6" spans="1:5">
+      <c r="A57" s="6"/>
       <c r="B57" s="2" t="s">
         <v>127</v>
       </c>
@@ -2234,7 +2225,7 @@
       <c r="D57" s="9"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" ht="16.5" spans="1:5">
+    <row r="58" ht="15.6" spans="1:5">
       <c r="A58" s="2" t="s">
         <v>128</v>
       </c>
@@ -2245,7 +2236,7 @@
       <c r="D58" s="9"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" ht="16.5" spans="1:5">
+    <row r="59" ht="15.6" spans="1:5">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>130</v>
@@ -2254,7 +2245,7 @@
       <c r="D59" s="9"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" ht="16.5" spans="1:5">
+    <row r="60" ht="15.6" spans="1:5">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>131</v>
@@ -2263,7 +2254,7 @@
       <c r="D60" s="9"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" ht="16.5" spans="1:5">
+    <row r="61" ht="15.6" spans="1:5">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>132</v>
@@ -2272,7 +2263,7 @@
       <c r="D61" s="9"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" ht="16.5" spans="1:5">
+    <row r="62" ht="15.6" spans="1:5">
       <c r="A62" s="2"/>
       <c r="B62" s="2" t="s">
         <v>133</v>
@@ -2281,7 +2272,7 @@
       <c r="D62" s="9"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" ht="16.5" spans="1:5">
+    <row r="63" ht="15.6" spans="1:5">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>134</v>
@@ -2290,7 +2281,7 @@
       <c r="D63" s="9"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" ht="16.5" spans="1:5">
+    <row r="64" ht="15.6" spans="1:5">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>135</v>
@@ -2299,7 +2290,7 @@
       <c r="D64" s="9"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" ht="16.5" spans="1:5">
+    <row r="65" ht="15.6" spans="1:5">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>136</v>
@@ -2308,7 +2299,7 @@
       <c r="D65" s="9"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" ht="16.5" spans="1:5">
+    <row r="66" ht="15.6" spans="1:5">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>137</v>
@@ -2317,7 +2308,7 @@
       <c r="D66" s="9"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" ht="16.5" spans="1:5">
+    <row r="67" ht="15.6" spans="1:5">
       <c r="A67" s="2"/>
       <c r="B67" s="2" t="s">
         <v>138</v>
@@ -2326,7 +2317,7 @@
       <c r="D67" s="9"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" ht="16.5" spans="1:5">
+    <row r="68" ht="15.6" spans="1:5">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>139</v>
@@ -2364,15 +2355,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="16.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="15.3611111111111" customWidth="1"/>
+    <col min="2" max="2" width="16.1851851851852" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="16.5462962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:4">
+    <row r="1" ht="16.2" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2386,7 +2377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:4">
+    <row r="2" ht="15.6" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2400,7 +2391,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:4">
+    <row r="3" ht="15.6" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>11</v>
@@ -2412,7 +2403,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:4">
+    <row r="4" ht="15.6" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -2420,9 +2411,11 @@
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:4">
+      <c r="D4" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" ht="15.6" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
@@ -2430,15 +2423,17 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" ht="16.5" spans="1:4">
+    <row r="6" ht="15.6" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:4">
+      <c r="D6" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
@@ -2448,7 +2443,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" ht="16.5" spans="1:4">
+    <row r="8" ht="15.6" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
@@ -2458,7 +2453,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" ht="16.5" spans="1:4">
+    <row r="9" ht="15.6" spans="1:4">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>40</v>
@@ -2466,7 +2461,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" ht="16.5" spans="1:4">
+    <row r="10" ht="15.6" spans="1:4">
       <c r="A10" s="4" t="s">
         <v>74</v>
       </c>
@@ -2478,7 +2473,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:4">
+    <row r="11" ht="15.6" spans="1:4">
       <c r="A11" s="5"/>
       <c r="B11" s="2" t="s">
         <v>70</v>
@@ -2486,7 +2481,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" ht="16.5" spans="1:4">
+    <row r="12" ht="15.6" spans="1:4">
       <c r="A12" s="5"/>
       <c r="B12" s="2" t="s">
         <v>141</v>
@@ -2494,7 +2489,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" ht="16.5" spans="1:4">
+    <row r="13" ht="15.6" spans="1:4">
       <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
         <v>55</v>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="143">
   <si>
     <t>一级菜单</t>
   </si>
@@ -478,6 +478,9 @@
   </si>
   <si>
     <t>√</t>
+  </si>
+  <si>
+    <t>产品BOM</t>
   </si>
   <si>
     <t>生产领料</t>
@@ -1183,7 +1186,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1192,6 +1195,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1562,12 +1574,12 @@
   <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.1296296296296" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.3703703703704" style="7" customWidth="1"/>
-    <col min="4" max="4" width="126.814814814815" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.4537037037037" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="13.75" style="10" customWidth="1"/>
+    <col min="2" max="2" width="22.1296296296296" style="10" customWidth="1"/>
+    <col min="3" max="3" width="27.3703703703704" style="10" customWidth="1"/>
+    <col min="4" max="4" width="126.814814814815" style="11" customWidth="1"/>
+    <col min="5" max="5" width="10.4537037037037" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.2" spans="1:5">
@@ -1597,10 +1609,10 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" ht="15.6" spans="1:5">
       <c r="A3" s="2"/>
@@ -1608,10 +1620,10 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" ht="15.6" spans="1:5">
       <c r="A4" s="2"/>
@@ -1621,10 +1633,10 @@
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" ht="15.6" spans="1:5">
       <c r="A5" s="2"/>
@@ -1632,34 +1644,34 @@
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" ht="15.6" spans="1:5">
       <c r="A6" s="2"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" ht="15.6" spans="1:5">
       <c r="A7" s="2"/>
-      <c r="B7" s="6"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" ht="15.6" spans="1:5">
       <c r="A8" s="2"/>
@@ -1667,10 +1679,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" ht="15.6" spans="1:5">
       <c r="A9" s="2"/>
@@ -1678,10 +1690,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" ht="15.6" spans="1:5">
       <c r="A10" s="2"/>
@@ -1689,10 +1701,10 @@
         <v>25</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" ht="15.6" spans="1:5">
       <c r="A11" s="2"/>
@@ -1700,10 +1712,10 @@
         <v>27</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" ht="15.6" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -1713,7 +1725,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="3"/>
@@ -1724,10 +1736,10 @@
         <v>32</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" ht="15.6" spans="1:5">
       <c r="A14" s="2"/>
@@ -1735,7 +1747,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="3"/>
@@ -1746,7 +1758,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
@@ -1757,7 +1769,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E16" s="3"/>
@@ -1768,7 +1780,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>41</v>
       </c>
       <c r="E17" s="3"/>
@@ -1779,7 +1791,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="3"/>
@@ -1790,89 +1802,89 @@
         <v>44</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" ht="15.6" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="12" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" ht="15.6" spans="1:5">
-      <c r="A21" s="5"/>
+      <c r="A21" s="8"/>
       <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" ht="15.6" spans="1:5">
-      <c r="A22" s="5"/>
+      <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" ht="15.6" spans="1:5">
-      <c r="A23" s="5"/>
+      <c r="A23" s="8"/>
       <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="10"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" ht="15.6" spans="1:5">
-      <c r="A24" s="5"/>
+      <c r="A24" s="8"/>
       <c r="B24" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="10"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" ht="15.6" spans="1:5">
-      <c r="A25" s="5"/>
+      <c r="A25" s="8"/>
       <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="10"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" ht="15.6" spans="1:5">
-      <c r="A26" s="6"/>
+      <c r="A26" s="9"/>
       <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="10"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" ht="15.6" spans="1:5">
       <c r="A27" s="2" t="s">
@@ -1882,7 +1894,7 @@
         <v>62</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="12" t="s">
         <v>63</v>
       </c>
       <c r="E27" s="3"/>
@@ -1893,7 +1905,7 @@
         <v>64</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="12" t="s">
         <v>65</v>
       </c>
       <c r="E28" s="3"/>
@@ -1904,7 +1916,7 @@
         <v>66</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="12" t="s">
         <v>67</v>
       </c>
       <c r="E29" s="3"/>
@@ -1915,7 +1927,7 @@
         <v>68</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="12" t="s">
         <v>69</v>
       </c>
       <c r="E30" s="3"/>
@@ -1926,7 +1938,7 @@
         <v>70</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="3"/>
@@ -1937,7 +1949,7 @@
         <v>72</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="15" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="3"/>
@@ -1950,7 +1962,7 @@
         <v>75</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="15" t="s">
         <v>76</v>
       </c>
       <c r="E33" s="3"/>
@@ -1961,7 +1973,7 @@
         <v>77</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="15" t="s">
         <v>78</v>
       </c>
       <c r="E34" s="3"/>
@@ -1972,7 +1984,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="15" t="s">
         <v>80</v>
       </c>
       <c r="E35" s="3"/>
@@ -1983,7 +1995,7 @@
         <v>81</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="15" t="s">
         <v>82</v>
       </c>
       <c r="E36" s="3"/>
@@ -1994,7 +2006,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="15" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="3"/>
@@ -2005,7 +2017,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="15" t="s">
         <v>86</v>
       </c>
       <c r="E38" s="3"/>
@@ -2014,140 +2026,140 @@
       <c r="A39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="12" t="s">
         <v>90</v>
       </c>
       <c r="E39" s="3"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:5">
       <c r="A40" s="2"/>
-      <c r="B40" s="5"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="12" t="s">
         <v>92</v>
       </c>
       <c r="E40" s="3"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:5">
       <c r="A41" s="2"/>
-      <c r="B41" s="6"/>
+      <c r="B41" s="9"/>
       <c r="C41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="12" t="s">
         <v>94</v>
       </c>
       <c r="E41" s="3"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:5">
       <c r="A42" s="2"/>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="12" t="s">
         <v>97</v>
       </c>
       <c r="E42" s="3"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:5">
       <c r="A43" s="2"/>
-      <c r="B43" s="5"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="12" t="s">
         <v>99</v>
       </c>
       <c r="E43" s="3"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:5">
       <c r="A44" s="2"/>
-      <c r="B44" s="5"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="12" t="s">
         <v>101</v>
       </c>
       <c r="E44" s="3"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:5">
       <c r="A45" s="2"/>
-      <c r="B45" s="6"/>
+      <c r="B45" s="9"/>
       <c r="C45" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="12" t="s">
         <v>103</v>
       </c>
       <c r="E45" s="3"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:5">
       <c r="A46" s="2"/>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="7" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="12" t="s">
         <v>106</v>
       </c>
       <c r="E46" s="3"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:5">
       <c r="A47" s="2"/>
-      <c r="B47" s="6"/>
+      <c r="B47" s="9"/>
       <c r="C47" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="12" t="s">
         <v>108</v>
       </c>
       <c r="E47" s="3"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:5">
       <c r="A48" s="2"/>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="12" t="s">
         <v>111</v>
       </c>
       <c r="E48" s="3"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:5">
       <c r="A49" s="2"/>
-      <c r="B49" s="5"/>
+      <c r="B49" s="8"/>
       <c r="C49" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E49" s="3"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:5">
       <c r="A50" s="2"/>
-      <c r="B50" s="6"/>
+      <c r="B50" s="9"/>
       <c r="C50" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E50" s="3"/>
@@ -2160,7 +2172,7 @@
         <v>117</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="12" t="s">
         <v>118</v>
       </c>
       <c r="E51" s="3"/>
@@ -2170,8 +2182,8 @@
       <c r="B52" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9" t="s">
+      <c r="C52" s="12"/>
+      <c r="D52" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E52" s="3"/>
@@ -2181,48 +2193,48 @@
       <c r="B53" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9" t="s">
+      <c r="C53" s="12"/>
+      <c r="D53" s="12" t="s">
         <v>122</v>
       </c>
       <c r="E53" s="3"/>
     </row>
     <row r="54" ht="15.6" spans="1:5">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="7" t="s">
         <v>123</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
       <c r="E54" s="3"/>
     </row>
     <row r="55" ht="15.6" spans="1:5">
-      <c r="A55" s="5"/>
+      <c r="A55" s="8"/>
       <c r="B55" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
       <c r="E55" s="3"/>
     </row>
     <row r="56" ht="15.6" spans="1:5">
-      <c r="A56" s="5"/>
+      <c r="A56" s="8"/>
       <c r="B56" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
       <c r="E56" s="3"/>
     </row>
     <row r="57" ht="15.6" spans="1:5">
-      <c r="A57" s="6"/>
+      <c r="A57" s="9"/>
       <c r="B57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
       <c r="E57" s="3"/>
     </row>
     <row r="58" ht="15.6" spans="1:5">
@@ -2232,8 +2244,8 @@
       <c r="B58" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
       <c r="E58" s="3"/>
     </row>
     <row r="59" ht="15.6" spans="1:5">
@@ -2242,7 +2254,7 @@
         <v>130</v>
       </c>
       <c r="C59" s="2"/>
-      <c r="D59" s="9"/>
+      <c r="D59" s="12"/>
       <c r="E59" s="3"/>
     </row>
     <row r="60" ht="15.6" spans="1:5">
@@ -2251,7 +2263,7 @@
         <v>131</v>
       </c>
       <c r="C60" s="2"/>
-      <c r="D60" s="9"/>
+      <c r="D60" s="12"/>
       <c r="E60" s="3"/>
     </row>
     <row r="61" ht="15.6" spans="1:5">
@@ -2260,7 +2272,7 @@
         <v>132</v>
       </c>
       <c r="C61" s="2"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="12"/>
       <c r="E61" s="3"/>
     </row>
     <row r="62" ht="15.6" spans="1:5">
@@ -2269,7 +2281,7 @@
         <v>133</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="9"/>
+      <c r="D62" s="12"/>
       <c r="E62" s="3"/>
     </row>
     <row r="63" ht="15.6" spans="1:5">
@@ -2278,7 +2290,7 @@
         <v>134</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="9"/>
+      <c r="D63" s="12"/>
       <c r="E63" s="3"/>
     </row>
     <row r="64" ht="15.6" spans="1:5">
@@ -2287,7 +2299,7 @@
         <v>135</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="9"/>
+      <c r="D64" s="12"/>
       <c r="E64" s="3"/>
     </row>
     <row r="65" ht="15.6" spans="1:5">
@@ -2296,7 +2308,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="9"/>
+      <c r="D65" s="12"/>
       <c r="E65" s="3"/>
     </row>
     <row r="66" ht="15.6" spans="1:5">
@@ -2305,7 +2317,7 @@
         <v>137</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="12"/>
       <c r="E66" s="3"/>
     </row>
     <row r="67" ht="15.6" spans="1:5">
@@ -2314,7 +2326,7 @@
         <v>138</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="12"/>
       <c r="E67" s="3"/>
     </row>
     <row r="68" ht="15.6" spans="1:5">
@@ -2323,7 +2335,7 @@
         <v>139</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="9"/>
+      <c r="D68" s="12"/>
       <c r="E68" s="3"/>
     </row>
   </sheetData>
@@ -2354,7 +2366,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.3611111111111" customWidth="1"/>
@@ -2405,7 +2417,7 @@
     </row>
     <row r="4" ht="15.6" spans="1:4">
       <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2417,92 +2429,102 @@
     </row>
     <row r="5" ht="15.6" spans="1:4">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="6" ht="15.6" spans="1:4">
       <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" ht="15.6" spans="1:4">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="7" ht="15.6" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
     </row>
     <row r="8" ht="15.6" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" ht="15.6" spans="1:4">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" ht="15.6" spans="1:4">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:4">
+      <c r="A11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="11" ht="15.6" spans="1:4">
-      <c r="A11" s="5"/>
-      <c r="B11" s="2" t="s">
+    <row r="12" ht="15.6" spans="1:4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:4">
-      <c r="A12" s="5"/>
-      <c r="B12" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" ht="15.6" spans="1:4">
-      <c r="A13" s="6"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
     </row>
+    <row r="14" ht="15.6" spans="1:4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B4:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="12200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="144">
   <si>
     <t>一级菜单</t>
   </si>
@@ -481,6 +481,9 @@
   </si>
   <si>
     <t>产品BOM</t>
+  </si>
+  <si>
+    <t>物料清单</t>
   </si>
   <si>
     <t>生产领料</t>
@@ -1186,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1195,15 +1198,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1572,17 +1566,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="10" customWidth="1"/>
-    <col min="2" max="2" width="22.1296296296296" style="10" customWidth="1"/>
-    <col min="3" max="3" width="27.3703703703704" style="10" customWidth="1"/>
-    <col min="4" max="4" width="126.814814814815" style="11" customWidth="1"/>
-    <col min="5" max="5" width="10.4537037037037" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
+    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" spans="1:5">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1599,7 +1593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:5">
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1609,23 +1603,23 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="3" ht="15.6" spans="1:5">
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="13"/>
-    </row>
-    <row r="4" ht="15.6" spans="1:5">
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -1633,91 +1627,91 @@
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" ht="15.6" spans="1:5">
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" ht="15.6" spans="1:5">
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="2"/>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" ht="15.6" spans="1:5">
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="2"/>
-      <c r="B7" s="9"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" ht="15.6" spans="1:5">
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14"/>
-    </row>
-    <row r="9" ht="15.6" spans="1:5">
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="10" ht="15.6" spans="1:5">
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:5">
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:5">
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1725,168 +1719,168 @@
         <v>30</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" ht="15.6" spans="1:5">
+    <row r="13" ht="16.5" spans="1:5">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:5">
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" ht="15.6" spans="1:5">
+    <row r="15" ht="16.5" spans="1:5">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" ht="15.6" spans="1:5">
+    <row r="16" ht="16.5" spans="1:5">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" ht="15.6" spans="1:5">
+    <row r="17" ht="16.5" spans="1:5">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" ht="15.6" spans="1:5">
+    <row r="18" ht="16.5" spans="1:5">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" ht="15.6" spans="1:5">
+    <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" ht="15.6" spans="1:5">
-      <c r="A20" s="7" t="s">
+    <row r="20" ht="16.5" spans="1:5">
+      <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" ht="15.6" spans="1:5">
-      <c r="A21" s="8"/>
+    <row r="21" ht="16.5" spans="1:5">
+      <c r="A21" s="5"/>
       <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" ht="15.6" spans="1:5">
-      <c r="A22" s="8"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:5">
+      <c r="A22" s="5"/>
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" ht="15.6" spans="1:5">
-      <c r="A23" s="8"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:5">
+      <c r="A23" s="5"/>
       <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" ht="15.6" spans="1:5">
-      <c r="A24" s="8"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:5">
+      <c r="A24" s="5"/>
       <c r="B24" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="13"/>
-    </row>
-    <row r="25" ht="15.6" spans="1:5">
-      <c r="A25" s="8"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:5">
+      <c r="A25" s="5"/>
       <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="13"/>
-    </row>
-    <row r="26" ht="15.6" spans="1:5">
-      <c r="A26" s="9"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:5">
+      <c r="A26" s="6"/>
       <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="13"/>
-    </row>
-    <row r="27" ht="15.6" spans="1:5">
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -1894,67 +1888,67 @@
         <v>62</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" ht="15.6" spans="1:5">
+    <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="9" t="s">
         <v>65</v>
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" ht="15.6" spans="1:5">
+    <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" ht="15.6" spans="1:5">
+    <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="9" t="s">
         <v>69</v>
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" ht="15.6" spans="1:5">
+    <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="12" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" ht="15.6" spans="1:5">
+    <row r="32" ht="16.5" spans="1:5">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" ht="15.6" spans="1:5">
+    <row r="33" ht="16.5" spans="1:5">
       <c r="A33" s="2" t="s">
         <v>74</v>
       </c>
@@ -1962,7 +1956,7 @@
         <v>75</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="12" t="s">
         <v>76</v>
       </c>
       <c r="E33" s="3"/>
@@ -1973,7 +1967,7 @@
         <v>77</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="12" t="s">
         <v>78</v>
       </c>
       <c r="E34" s="3"/>
@@ -1984,7 +1978,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="12" t="s">
         <v>80</v>
       </c>
       <c r="E35" s="3"/>
@@ -1995,7 +1989,7 @@
         <v>81</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E36" s="3"/>
@@ -2006,7 +2000,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="12" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="3"/>
@@ -2017,7 +2011,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E38" s="3"/>
@@ -2026,140 +2020,140 @@
       <c r="A39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E39" s="3"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:5">
       <c r="A40" s="2"/>
-      <c r="B40" s="8"/>
+      <c r="B40" s="5"/>
       <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="9" t="s">
         <v>92</v>
       </c>
       <c r="E40" s="3"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:5">
       <c r="A41" s="2"/>
-      <c r="B41" s="9"/>
+      <c r="B41" s="6"/>
       <c r="C41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="9" t="s">
         <v>94</v>
       </c>
       <c r="E41" s="3"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:5">
       <c r="A42" s="2"/>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E42" s="3"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:5">
       <c r="A43" s="2"/>
-      <c r="B43" s="8"/>
+      <c r="B43" s="5"/>
       <c r="C43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E43" s="3"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:5">
       <c r="A44" s="2"/>
-      <c r="B44" s="8"/>
+      <c r="B44" s="5"/>
       <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="9" t="s">
         <v>101</v>
       </c>
       <c r="E44" s="3"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:5">
       <c r="A45" s="2"/>
-      <c r="B45" s="9"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="9" t="s">
         <v>103</v>
       </c>
       <c r="E45" s="3"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:5">
       <c r="A46" s="2"/>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="4" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="9" t="s">
         <v>106</v>
       </c>
       <c r="E46" s="3"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:5">
       <c r="A47" s="2"/>
-      <c r="B47" s="9"/>
+      <c r="B47" s="6"/>
       <c r="C47" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E47" s="3"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:5">
       <c r="A48" s="2"/>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E48" s="3"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:5">
       <c r="A49" s="2"/>
-      <c r="B49" s="8"/>
+      <c r="B49" s="5"/>
       <c r="C49" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E49" s="3"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:5">
       <c r="A50" s="2"/>
-      <c r="B50" s="9"/>
+      <c r="B50" s="6"/>
       <c r="C50" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="9" t="s">
         <v>115</v>
       </c>
       <c r="E50" s="3"/>
@@ -2172,170 +2166,170 @@
         <v>117</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="9" t="s">
         <v>118</v>
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" ht="15.6" spans="1:5">
+    <row r="52" ht="16.5" spans="1:5">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12" t="s">
+      <c r="C52" s="9"/>
+      <c r="D52" s="9" t="s">
         <v>120</v>
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" ht="15.6" spans="1:5">
+    <row r="53" ht="16.5" spans="1:5">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12" t="s">
+      <c r="C53" s="9"/>
+      <c r="D53" s="9" t="s">
         <v>122</v>
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" ht="15.6" spans="1:5">
-      <c r="A54" s="7" t="s">
+    <row r="54" ht="16.5" spans="1:5">
+      <c r="A54" s="4" t="s">
         <v>123</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" ht="15.6" spans="1:5">
-      <c r="A55" s="8"/>
+    <row r="55" ht="16.5" spans="1:5">
+      <c r="A55" s="5"/>
       <c r="B55" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" ht="15.6" spans="1:5">
-      <c r="A56" s="8"/>
+    <row r="56" ht="16.5" spans="1:5">
+      <c r="A56" s="5"/>
       <c r="B56" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" ht="15.6" spans="1:5">
-      <c r="A57" s="9"/>
+    <row r="57" ht="16.5" spans="1:5">
+      <c r="A57" s="6"/>
       <c r="B57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" ht="15.6" spans="1:5">
+    <row r="58" ht="16.5" spans="1:5">
       <c r="A58" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" ht="15.6" spans="1:5">
+    <row r="59" ht="16.5" spans="1:5">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C59" s="2"/>
-      <c r="D59" s="12"/>
+      <c r="D59" s="9"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" ht="15.6" spans="1:5">
+    <row r="60" ht="16.5" spans="1:5">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C60" s="2"/>
-      <c r="D60" s="12"/>
+      <c r="D60" s="9"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" ht="15.6" spans="1:5">
+    <row r="61" ht="16.5" spans="1:5">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C61" s="2"/>
-      <c r="D61" s="12"/>
+      <c r="D61" s="9"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" ht="15.6" spans="1:5">
+    <row r="62" ht="16.5" spans="1:5">
       <c r="A62" s="2"/>
       <c r="B62" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="12"/>
+      <c r="D62" s="9"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" ht="15.6" spans="1:5">
+    <row r="63" ht="16.5" spans="1:5">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="12"/>
+      <c r="D63" s="9"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" ht="15.6" spans="1:5">
+    <row r="64" ht="16.5" spans="1:5">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="12"/>
+      <c r="D64" s="9"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" ht="15.6" spans="1:5">
+    <row r="65" ht="16.5" spans="1:5">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="12"/>
+      <c r="D65" s="9"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" ht="15.6" spans="1:5">
+    <row r="66" ht="16.5" spans="1:5">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="12"/>
+      <c r="D66" s="9"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" ht="15.6" spans="1:5">
+    <row r="67" ht="16.5" spans="1:5">
       <c r="A67" s="2"/>
       <c r="B67" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="12"/>
+      <c r="D67" s="9"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" ht="15.6" spans="1:5">
+    <row r="68" ht="16.5" spans="1:5">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="12"/>
+      <c r="D68" s="9"/>
       <c r="E68" s="3"/>
     </row>
   </sheetData>
@@ -2366,16 +2360,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.3611111111111" customWidth="1"/>
-    <col min="2" max="2" width="16.1851851851852" customWidth="1"/>
+    <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="16.1818181818182" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16.5462962962963" customWidth="1"/>
+    <col min="4" max="4" width="16.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" spans="1:4">
+    <row r="1" ht="16.5" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2389,7 +2383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:4">
+    <row r="2" ht="16.5" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2403,7 +2397,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" ht="15.6" spans="1:4">
+    <row r="3" ht="16.5" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>11</v>
@@ -2415,7 +2409,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" ht="15.6" spans="1:4">
+    <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -2427,7 +2421,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" ht="15.6" spans="1:4">
+    <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
@@ -2437,15 +2431,17 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" ht="15.6" spans="1:4">
+    <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="6"/>
       <c r="C6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" ht="15.6" spans="1:4">
+      <c r="D6" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -2455,7 +2451,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" ht="15.6" spans="1:4">
+    <row r="8" ht="16.5" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -2463,9 +2459,11 @@
         <v>51</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" ht="15.6" spans="1:4">
+      <c r="D8" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2475,55 +2473,63 @@
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" ht="15.6" spans="1:4">
+    <row r="10" ht="16.5" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" ht="15.6" spans="1:4">
-      <c r="A11" s="7" t="s">
+    <row r="11" ht="16.5" spans="1:4">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="12" ht="15.6" spans="1:4">
-      <c r="A12" s="8"/>
-      <c r="B12" s="2" t="s">
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:4">
-      <c r="A13" s="8"/>
-      <c r="B13" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" ht="15.6" spans="1:4">
-      <c r="A14" s="9"/>
+    <row r="14" ht="16.5" spans="1:4">
+      <c r="A14" s="5"/>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="3"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:4">
+      <c r="A15" s="6"/>
+      <c r="B15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A15"/>
     <mergeCell ref="B4:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12200" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="12935" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="144">
   <si>
     <t>一级菜单</t>
   </si>
@@ -1566,17 +1566,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
-    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
+    <col min="1" max="1" width="13.75" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.1296296296296" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.3703703703704" style="7" customWidth="1"/>
+    <col min="4" max="4" width="126.814814814815" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.4537037037037" style="7" customWidth="1"/>
     <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
+    <row r="1" ht="16.2" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:5">
+    <row r="2" ht="15.6" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="E2" s="10"/>
     </row>
-    <row r="3" ht="16.5" spans="1:5">
+    <row r="3" ht="15.6" spans="1:5">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E3" s="10"/>
     </row>
-    <row r="4" ht="16.5" spans="1:5">
+    <row r="4" ht="15.6" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" ht="16.5" spans="1:5">
+    <row r="5" ht="15.6" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" ht="16.5" spans="1:5">
+    <row r="6" ht="15.6" spans="1:5">
       <c r="A6" s="2"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" ht="16.5" spans="1:5">
+    <row r="7" ht="15.6" spans="1:5">
       <c r="A7" s="2"/>
       <c r="B7" s="6"/>
       <c r="C7" s="2" t="s">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" ht="16.5" spans="1:5">
+    <row r="8" ht="15.6" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>21</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" ht="16.5" spans="1:5">
+    <row r="9" ht="15.6" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>23</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" ht="16.5" spans="1:5">
+    <row r="10" ht="15.6" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>25</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" ht="16.5" spans="1:5">
+    <row r="11" ht="15.6" spans="1:5">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" ht="16.5" spans="1:5">
+    <row r="12" ht="15.6" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" ht="16.5" spans="1:5">
+    <row r="13" ht="15.6" spans="1:5">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>32</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" ht="16.5" spans="1:5">
+    <row r="14" ht="15.6" spans="1:5">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>34</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" ht="16.5" spans="1:5">
+    <row r="15" ht="15.6" spans="1:5">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>36</v>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" ht="16.5" spans="1:5">
+    <row r="16" ht="15.6" spans="1:5">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>38</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" ht="16.5" spans="1:5">
+    <row r="17" ht="15.6" spans="1:5">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>40</v>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" ht="16.5" spans="1:5">
+    <row r="18" ht="15.6" spans="1:5">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>42</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" ht="16.5" spans="1:5">
+    <row r="19" ht="15.6" spans="1:5">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>44</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" ht="16.5" spans="1:5">
+    <row r="20" ht="15.6" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" ht="16.5" spans="1:5">
+    <row r="21" ht="15.6" spans="1:5">
       <c r="A21" s="5"/>
       <c r="B21" s="2" t="s">
         <v>49</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" ht="16.5" spans="1:5">
+    <row r="22" ht="15.6" spans="1:5">
       <c r="A22" s="5"/>
       <c r="B22" s="2" t="s">
         <v>51</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E22" s="10"/>
     </row>
-    <row r="23" ht="16.5" spans="1:5">
+    <row r="23" ht="15.6" spans="1:5">
       <c r="A23" s="5"/>
       <c r="B23" s="2" t="s">
         <v>53</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" ht="16.5" spans="1:5">
+    <row r="24" ht="15.6" spans="1:5">
       <c r="A24" s="5"/>
       <c r="B24" s="2" t="s">
         <v>55</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" ht="16.5" spans="1:5">
+    <row r="25" ht="15.6" spans="1:5">
       <c r="A25" s="5"/>
       <c r="B25" s="2" t="s">
         <v>57</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E25" s="10"/>
     </row>
-    <row r="26" ht="16.5" spans="1:5">
+    <row r="26" ht="15.6" spans="1:5">
       <c r="A26" s="6"/>
       <c r="B26" s="2" t="s">
         <v>59</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E26" s="10"/>
     </row>
-    <row r="27" ht="16.5" spans="1:5">
+    <row r="27" ht="15.6" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" ht="16.5" spans="1:5">
+    <row r="28" ht="15.6" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>64</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" ht="16.5" spans="1:5">
+    <row r="29" ht="15.6" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>66</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" ht="16.5" spans="1:5">
+    <row r="30" ht="15.6" spans="1:5">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>68</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" ht="16.5" spans="1:5">
+    <row r="31" ht="15.6" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>70</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" ht="16.5" spans="1:5">
+    <row r="32" ht="15.6" spans="1:5">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>72</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" ht="16.5" spans="1:5">
+    <row r="33" ht="15.6" spans="1:5">
       <c r="A33" s="2" t="s">
         <v>74</v>
       </c>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" ht="16.5" spans="1:5">
+    <row r="52" ht="15.6" spans="1:5">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>119</v>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" ht="16.5" spans="1:5">
+    <row r="53" ht="15.6" spans="1:5">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>121</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" ht="16.5" spans="1:5">
+    <row r="54" ht="15.6" spans="1:5">
       <c r="A54" s="4" t="s">
         <v>123</v>
       </c>
@@ -2204,7 +2204,7 @@
       <c r="D54" s="9"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" ht="16.5" spans="1:5">
+    <row r="55" ht="15.6" spans="1:5">
       <c r="A55" s="5"/>
       <c r="B55" s="2" t="s">
         <v>125</v>
@@ -2213,7 +2213,7 @@
       <c r="D55" s="9"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" ht="16.5" spans="1:5">
+    <row r="56" ht="15.6" spans="1:5">
       <c r="A56" s="5"/>
       <c r="B56" s="2" t="s">
         <v>126</v>
@@ -2222,7 +2222,7 @@
       <c r="D56" s="9"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" ht="16.5" spans="1:5">
+    <row r="57" ht="15.6" spans="1:5">
       <c r="A57" s="6"/>
       <c r="B57" s="2" t="s">
         <v>127</v>
@@ -2231,7 +2231,7 @@
       <c r="D57" s="9"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" ht="16.5" spans="1:5">
+    <row r="58" ht="15.6" spans="1:5">
       <c r="A58" s="2" t="s">
         <v>128</v>
       </c>
@@ -2242,7 +2242,7 @@
       <c r="D58" s="9"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" ht="16.5" spans="1:5">
+    <row r="59" ht="15.6" spans="1:5">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>130</v>
@@ -2251,7 +2251,7 @@
       <c r="D59" s="9"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" ht="16.5" spans="1:5">
+    <row r="60" ht="15.6" spans="1:5">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>131</v>
@@ -2260,7 +2260,7 @@
       <c r="D60" s="9"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" ht="16.5" spans="1:5">
+    <row r="61" ht="15.6" spans="1:5">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>132</v>
@@ -2269,7 +2269,7 @@
       <c r="D61" s="9"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" ht="16.5" spans="1:5">
+    <row r="62" ht="15.6" spans="1:5">
       <c r="A62" s="2"/>
       <c r="B62" s="2" t="s">
         <v>133</v>
@@ -2278,7 +2278,7 @@
       <c r="D62" s="9"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" ht="16.5" spans="1:5">
+    <row r="63" ht="15.6" spans="1:5">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>134</v>
@@ -2287,7 +2287,7 @@
       <c r="D63" s="9"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" ht="16.5" spans="1:5">
+    <row r="64" ht="15.6" spans="1:5">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>135</v>
@@ -2296,7 +2296,7 @@
       <c r="D64" s="9"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" ht="16.5" spans="1:5">
+    <row r="65" ht="15.6" spans="1:5">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>136</v>
@@ -2305,7 +2305,7 @@
       <c r="D65" s="9"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" ht="16.5" spans="1:5">
+    <row r="66" ht="15.6" spans="1:5">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>137</v>
@@ -2314,7 +2314,7 @@
       <c r="D66" s="9"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" ht="16.5" spans="1:5">
+    <row r="67" ht="15.6" spans="1:5">
       <c r="A67" s="2"/>
       <c r="B67" s="2" t="s">
         <v>138</v>
@@ -2323,7 +2323,7 @@
       <c r="D67" s="9"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" ht="16.5" spans="1:5">
+    <row r="68" ht="15.6" spans="1:5">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>139</v>
@@ -2361,15 +2361,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="16.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="15.3611111111111" customWidth="1"/>
+    <col min="2" max="2" width="16.1851851851852" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="16.5462962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:4">
+    <row r="1" ht="16.2" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:4">
+    <row r="2" ht="15.6" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:4">
+    <row r="3" ht="15.6" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>11</v>
@@ -2409,7 +2409,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:4">
+    <row r="4" ht="15.6" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -2421,7 +2421,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:4">
+    <row r="5" ht="15.6" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
@@ -2431,7 +2431,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:4">
+    <row r="6" ht="15.6" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="6"/>
       <c r="C6" s="2" t="s">
@@ -2441,7 +2441,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:4">
+    <row r="7" ht="15.6" spans="1:4">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -2451,7 +2451,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:4">
+    <row r="8" ht="15.6" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:4">
+    <row r="9" ht="15.6" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2471,17 +2471,21 @@
         <v>30</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
+      <c r="D9" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" ht="15.6" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
+      <c r="D10" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" ht="15.6" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>40</v>
@@ -2489,7 +2493,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" ht="16.5" spans="1:4">
+    <row r="12" ht="15.6" spans="1:4">
       <c r="A12" s="4" t="s">
         <v>74</v>
       </c>
@@ -2501,7 +2505,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:4">
+    <row r="13" ht="15.6" spans="1:4">
       <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
         <v>70</v>
@@ -2509,7 +2513,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" ht="16.5" spans="1:4">
+    <row r="14" ht="15.6" spans="1:4">
       <c r="A14" s="5"/>
       <c r="B14" s="2" t="s">
         <v>143</v>
@@ -2517,7 +2521,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" ht="16.5" spans="1:4">
+    <row r="15" ht="15.6" spans="1:4">
       <c r="A15" s="6"/>
       <c r="B15" s="2" t="s">
         <v>55</v>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="12935" activeTab="1"/>
+    <workbookView windowWidth="17220" windowHeight="11600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="144">
   <si>
     <t>一级菜单</t>
   </si>
@@ -1566,17 +1566,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.1296296296296" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.3703703703704" style="7" customWidth="1"/>
-    <col min="4" max="4" width="126.814814814815" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.4537037037037" style="7" customWidth="1"/>
+    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
+    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
     <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" spans="1:5">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:5">
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="E2" s="10"/>
     </row>
-    <row r="3" ht="15.6" spans="1:5">
+    <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E3" s="10"/>
     </row>
-    <row r="4" ht="15.6" spans="1:5">
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" ht="15.6" spans="1:5">
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" ht="15.6" spans="1:5">
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="2"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" ht="15.6" spans="1:5">
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="2"/>
       <c r="B7" s="6"/>
       <c r="C7" s="2" t="s">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" ht="15.6" spans="1:5">
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>21</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" ht="15.6" spans="1:5">
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>23</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" ht="15.6" spans="1:5">
+    <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>25</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" ht="15.6" spans="1:5">
+    <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" ht="15.6" spans="1:5">
+    <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" ht="15.6" spans="1:5">
+    <row r="13" ht="16.5" spans="1:5">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>32</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" ht="15.6" spans="1:5">
+    <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>34</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" ht="15.6" spans="1:5">
+    <row r="15" ht="16.5" spans="1:5">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>36</v>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" ht="15.6" spans="1:5">
+    <row r="16" ht="16.5" spans="1:5">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>38</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" ht="15.6" spans="1:5">
+    <row r="17" ht="16.5" spans="1:5">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>40</v>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" ht="15.6" spans="1:5">
+    <row r="18" ht="16.5" spans="1:5">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>42</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" ht="15.6" spans="1:5">
+    <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>44</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" ht="15.6" spans="1:5">
+    <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" ht="15.6" spans="1:5">
+    <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="5"/>
       <c r="B21" s="2" t="s">
         <v>49</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" ht="15.6" spans="1:5">
+    <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="5"/>
       <c r="B22" s="2" t="s">
         <v>51</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E22" s="10"/>
     </row>
-    <row r="23" ht="15.6" spans="1:5">
+    <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="5"/>
       <c r="B23" s="2" t="s">
         <v>53</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" ht="15.6" spans="1:5">
+    <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="5"/>
       <c r="B24" s="2" t="s">
         <v>55</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" ht="15.6" spans="1:5">
+    <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="5"/>
       <c r="B25" s="2" t="s">
         <v>57</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E25" s="10"/>
     </row>
-    <row r="26" ht="15.6" spans="1:5">
+    <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="6"/>
       <c r="B26" s="2" t="s">
         <v>59</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E26" s="10"/>
     </row>
-    <row r="27" ht="15.6" spans="1:5">
+    <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" ht="15.6" spans="1:5">
+    <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>64</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" ht="15.6" spans="1:5">
+    <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>66</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" ht="15.6" spans="1:5">
+    <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>68</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" ht="15.6" spans="1:5">
+    <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>70</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" ht="15.6" spans="1:5">
+    <row r="32" ht="16.5" spans="1:5">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>72</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" ht="15.6" spans="1:5">
+    <row r="33" ht="16.5" spans="1:5">
       <c r="A33" s="2" t="s">
         <v>74</v>
       </c>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" ht="15.6" spans="1:5">
+    <row r="52" ht="16.5" spans="1:5">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>119</v>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" ht="15.6" spans="1:5">
+    <row r="53" ht="16.5" spans="1:5">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>121</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" ht="15.6" spans="1:5">
+    <row r="54" ht="16.5" spans="1:5">
       <c r="A54" s="4" t="s">
         <v>123</v>
       </c>
@@ -2204,7 +2204,7 @@
       <c r="D54" s="9"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" ht="15.6" spans="1:5">
+    <row r="55" ht="16.5" spans="1:5">
       <c r="A55" s="5"/>
       <c r="B55" s="2" t="s">
         <v>125</v>
@@ -2213,7 +2213,7 @@
       <c r="D55" s="9"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" ht="15.6" spans="1:5">
+    <row r="56" ht="16.5" spans="1:5">
       <c r="A56" s="5"/>
       <c r="B56" s="2" t="s">
         <v>126</v>
@@ -2222,7 +2222,7 @@
       <c r="D56" s="9"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" ht="15.6" spans="1:5">
+    <row r="57" ht="16.5" spans="1:5">
       <c r="A57" s="6"/>
       <c r="B57" s="2" t="s">
         <v>127</v>
@@ -2231,7 +2231,7 @@
       <c r="D57" s="9"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" ht="15.6" spans="1:5">
+    <row r="58" ht="16.5" spans="1:5">
       <c r="A58" s="2" t="s">
         <v>128</v>
       </c>
@@ -2242,7 +2242,7 @@
       <c r="D58" s="9"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" ht="15.6" spans="1:5">
+    <row r="59" ht="16.5" spans="1:5">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>130</v>
@@ -2251,7 +2251,7 @@
       <c r="D59" s="9"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" ht="15.6" spans="1:5">
+    <row r="60" ht="16.5" spans="1:5">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>131</v>
@@ -2260,7 +2260,7 @@
       <c r="D60" s="9"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" ht="15.6" spans="1:5">
+    <row r="61" ht="16.5" spans="1:5">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>132</v>
@@ -2269,7 +2269,7 @@
       <c r="D61" s="9"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" ht="15.6" spans="1:5">
+    <row r="62" ht="16.5" spans="1:5">
       <c r="A62" s="2"/>
       <c r="B62" s="2" t="s">
         <v>133</v>
@@ -2278,7 +2278,7 @@
       <c r="D62" s="9"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" ht="15.6" spans="1:5">
+    <row r="63" ht="16.5" spans="1:5">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>134</v>
@@ -2287,7 +2287,7 @@
       <c r="D63" s="9"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" ht="15.6" spans="1:5">
+    <row r="64" ht="16.5" spans="1:5">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>135</v>
@@ -2296,7 +2296,7 @@
       <c r="D64" s="9"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" ht="15.6" spans="1:5">
+    <row r="65" ht="16.5" spans="1:5">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>136</v>
@@ -2305,7 +2305,7 @@
       <c r="D65" s="9"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" ht="15.6" spans="1:5">
+    <row r="66" ht="16.5" spans="1:5">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>137</v>
@@ -2314,7 +2314,7 @@
       <c r="D66" s="9"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" ht="15.6" spans="1:5">
+    <row r="67" ht="16.5" spans="1:5">
       <c r="A67" s="2"/>
       <c r="B67" s="2" t="s">
         <v>138</v>
@@ -2323,7 +2323,7 @@
       <c r="D67" s="9"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" ht="15.6" spans="1:5">
+    <row r="68" ht="16.5" spans="1:5">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>139</v>
@@ -2361,15 +2361,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.3611111111111" customWidth="1"/>
-    <col min="2" max="2" width="16.1851851851852" customWidth="1"/>
+    <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="16.1818181818182" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16.5462962962963" customWidth="1"/>
+    <col min="4" max="4" width="16.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" spans="1:4">
+    <row r="1" ht="16.5" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:4">
+    <row r="2" ht="16.5" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" ht="15.6" spans="1:4">
+    <row r="3" ht="16.5" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>11</v>
@@ -2409,7 +2409,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" ht="15.6" spans="1:4">
+    <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -2421,7 +2421,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" ht="15.6" spans="1:4">
+    <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
@@ -2431,7 +2431,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" ht="15.6" spans="1:4">
+    <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="6"/>
       <c r="C6" s="2" t="s">
@@ -2441,7 +2441,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" ht="15.6" spans="1:4">
+    <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -2451,7 +2451,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" ht="15.6" spans="1:4">
+    <row r="8" ht="16.5" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" ht="15.6" spans="1:4">
+    <row r="9" ht="16.5" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" ht="15.6" spans="1:4">
+    <row r="10" ht="16.5" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>142</v>
@@ -2485,7 +2485,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="11" ht="15.6" spans="1:4">
+    <row r="11" ht="16.5" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>40</v>
@@ -2493,7 +2493,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" ht="15.6" spans="1:4">
+    <row r="12" ht="16.5" spans="1:4">
       <c r="A12" s="4" t="s">
         <v>74</v>
       </c>
@@ -2505,15 +2505,17 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" ht="15.6" spans="1:4">
+    <row r="13" ht="16.5" spans="1:4">
       <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:4">
+      <c r="D13" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="5"/>
       <c r="B14" s="2" t="s">
         <v>143</v>
@@ -2521,7 +2523,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" ht="15.6" spans="1:4">
+    <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="6"/>
       <c r="B15" s="2" t="s">
         <v>55</v>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17220" windowHeight="11600" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="12200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="152">
   <si>
     <t>一级菜单</t>
   </si>
@@ -486,7 +486,31 @@
     <t>物料清单</t>
   </si>
   <si>
+    <t>生成工单</t>
+  </si>
+  <si>
     <t>生产领料</t>
+  </si>
+  <si>
+    <t>到货通知</t>
+  </si>
+  <si>
+    <t>库存清单</t>
+  </si>
+  <si>
+    <t>生产排班</t>
+  </si>
+  <si>
+    <t>生产工人档案</t>
+  </si>
+  <si>
+    <t>排班明细</t>
+  </si>
+  <si>
+    <t>考勤管理</t>
+  </si>
+  <si>
+    <t>考勤记录</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1213,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1205,6 +1229,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1568,12 +1595,12 @@
   <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
-    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="13.7545454545455" style="8" customWidth="1"/>
+    <col min="2" max="2" width="22.1272727272727" style="8" customWidth="1"/>
+    <col min="3" max="3" width="27.3727272727273" style="8" customWidth="1"/>
+    <col min="4" max="4" width="126.818181818182" style="9" customWidth="1"/>
+    <col min="5" max="5" width="10.4545454545455" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
@@ -1603,10 +1630,10 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2"/>
@@ -1614,10 +1641,10 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="2"/>
@@ -1627,10 +1654,10 @@
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="2"/>
@@ -1638,10 +1665,10 @@
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="11"/>
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="2"/>
@@ -1651,10 +1678,10 @@
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="2"/>
@@ -1662,10 +1689,10 @@
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="2"/>
@@ -1673,10 +1700,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="2"/>
@@ -1684,10 +1711,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="2"/>
@@ -1695,10 +1722,10 @@
         <v>25</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="2"/>
@@ -1706,10 +1733,10 @@
         <v>27</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -1719,7 +1746,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="3"/>
@@ -1730,10 +1757,10 @@
         <v>32</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="2"/>
@@ -1741,7 +1768,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="3"/>
@@ -1752,7 +1779,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
@@ -1763,7 +1790,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="E16" s="3"/>
@@ -1774,7 +1801,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E17" s="3"/>
@@ -1785,7 +1812,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="3"/>
@@ -1796,7 +1823,7 @@
         <v>44</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="3"/>
@@ -1809,7 +1836,7 @@
         <v>47</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3"/>
@@ -1820,10 +1847,10 @@
         <v>49</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="5"/>
@@ -1831,10 +1858,10 @@
         <v>51</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="5"/>
@@ -1842,10 +1869,10 @@
         <v>53</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="10"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="5"/>
@@ -1853,10 +1880,10 @@
         <v>55</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="10"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="5"/>
@@ -1864,10 +1891,10 @@
         <v>57</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="10"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="6"/>
@@ -1875,10 +1902,10 @@
         <v>59</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="10"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="2" t="s">
@@ -1888,7 +1915,7 @@
         <v>62</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E27" s="3"/>
@@ -1899,7 +1926,7 @@
         <v>64</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E28" s="3"/>
@@ -1910,7 +1937,7 @@
         <v>66</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E29" s="3"/>
@@ -1921,7 +1948,7 @@
         <v>68</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E30" s="3"/>
@@ -1932,7 +1959,7 @@
         <v>70</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="3"/>
@@ -1943,7 +1970,7 @@
         <v>72</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="13" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="3"/>
@@ -1956,7 +1983,7 @@
         <v>75</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="13" t="s">
         <v>76</v>
       </c>
       <c r="E33" s="3"/>
@@ -1967,7 +1994,7 @@
         <v>77</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="13" t="s">
         <v>78</v>
       </c>
       <c r="E34" s="3"/>
@@ -1978,7 +2005,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>80</v>
       </c>
       <c r="E35" s="3"/>
@@ -1989,7 +2016,7 @@
         <v>81</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>82</v>
       </c>
       <c r="E36" s="3"/>
@@ -2000,7 +2027,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="13" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="3"/>
@@ -2011,7 +2038,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>86</v>
       </c>
       <c r="E38" s="3"/>
@@ -2026,7 +2053,7 @@
       <c r="C39" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E39" s="3"/>
@@ -2037,7 +2064,7 @@
       <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E40" s="3"/>
@@ -2048,7 +2075,7 @@
       <c r="C41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="10" t="s">
         <v>94</v>
       </c>
       <c r="E41" s="3"/>
@@ -2061,7 +2088,7 @@
       <c r="C42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="10" t="s">
         <v>97</v>
       </c>
       <c r="E42" s="3"/>
@@ -2072,7 +2099,7 @@
       <c r="C43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="10" t="s">
         <v>99</v>
       </c>
       <c r="E43" s="3"/>
@@ -2083,7 +2110,7 @@
       <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="10" t="s">
         <v>101</v>
       </c>
       <c r="E44" s="3"/>
@@ -2094,7 +2121,7 @@
       <c r="C45" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="10" t="s">
         <v>103</v>
       </c>
       <c r="E45" s="3"/>
@@ -2107,7 +2134,7 @@
       <c r="C46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E46" s="3"/>
@@ -2118,7 +2145,7 @@
       <c r="C47" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="10" t="s">
         <v>108</v>
       </c>
       <c r="E47" s="3"/>
@@ -2131,7 +2158,7 @@
       <c r="C48" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="10" t="s">
         <v>111</v>
       </c>
       <c r="E48" s="3"/>
@@ -2142,7 +2169,7 @@
       <c r="C49" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="10" t="s">
         <v>113</v>
       </c>
       <c r="E49" s="3"/>
@@ -2153,7 +2180,7 @@
       <c r="C50" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="10" t="s">
         <v>115</v>
       </c>
       <c r="E50" s="3"/>
@@ -2166,7 +2193,7 @@
         <v>117</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="10" t="s">
         <v>118</v>
       </c>
       <c r="E51" s="3"/>
@@ -2176,8 +2203,8 @@
       <c r="B52" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9" t="s">
+      <c r="C52" s="10"/>
+      <c r="D52" s="10" t="s">
         <v>120</v>
       </c>
       <c r="E52" s="3"/>
@@ -2187,8 +2214,8 @@
       <c r="B53" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9" t="s">
+      <c r="C53" s="10"/>
+      <c r="D53" s="10" t="s">
         <v>122</v>
       </c>
       <c r="E53" s="3"/>
@@ -2200,8 +2227,8 @@
       <c r="B54" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
       <c r="E54" s="3"/>
     </row>
     <row r="55" ht="16.5" spans="1:5">
@@ -2209,8 +2236,8 @@
       <c r="B55" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
       <c r="E55" s="3"/>
     </row>
     <row r="56" ht="16.5" spans="1:5">
@@ -2218,8 +2245,8 @@
       <c r="B56" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="3"/>
     </row>
     <row r="57" ht="16.5" spans="1:5">
@@ -2227,8 +2254,8 @@
       <c r="B57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
       <c r="E57" s="3"/>
     </row>
     <row r="58" ht="16.5" spans="1:5">
@@ -2238,8 +2265,8 @@
       <c r="B58" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
       <c r="E58" s="3"/>
     </row>
     <row r="59" ht="16.5" spans="1:5">
@@ -2248,7 +2275,7 @@
         <v>130</v>
       </c>
       <c r="C59" s="2"/>
-      <c r="D59" s="9"/>
+      <c r="D59" s="10"/>
       <c r="E59" s="3"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
@@ -2257,7 +2284,7 @@
         <v>131</v>
       </c>
       <c r="C60" s="2"/>
-      <c r="D60" s="9"/>
+      <c r="D60" s="10"/>
       <c r="E60" s="3"/>
     </row>
     <row r="61" ht="16.5" spans="1:5">
@@ -2266,7 +2293,7 @@
         <v>132</v>
       </c>
       <c r="C61" s="2"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="10"/>
       <c r="E61" s="3"/>
     </row>
     <row r="62" ht="16.5" spans="1:5">
@@ -2275,7 +2302,7 @@
         <v>133</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="9"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="3"/>
     </row>
     <row r="63" ht="16.5" spans="1:5">
@@ -2284,7 +2311,7 @@
         <v>134</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="9"/>
+      <c r="D63" s="10"/>
       <c r="E63" s="3"/>
     </row>
     <row r="64" ht="16.5" spans="1:5">
@@ -2293,7 +2320,7 @@
         <v>135</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="9"/>
+      <c r="D64" s="10"/>
       <c r="E64" s="3"/>
     </row>
     <row r="65" ht="16.5" spans="1:5">
@@ -2302,7 +2329,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="9"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="3"/>
     </row>
     <row r="66" ht="16.5" spans="1:5">
@@ -2311,7 +2338,7 @@
         <v>137</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="10"/>
       <c r="E66" s="3"/>
     </row>
     <row r="67" ht="16.5" spans="1:5">
@@ -2320,7 +2347,7 @@
         <v>138</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="10"/>
       <c r="E67" s="3"/>
     </row>
     <row r="68" ht="16.5" spans="1:5">
@@ -2329,7 +2356,7 @@
         <v>139</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="9"/>
+      <c r="D68" s="10"/>
       <c r="E68" s="3"/>
     </row>
   </sheetData>
@@ -2360,7 +2387,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
@@ -2488,27 +2515,27 @@
     <row r="11" ht="16.5" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:4">
-      <c r="A12" s="4" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:4">
-      <c r="A13" s="5"/>
-      <c r="B13" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="3" t="s">
@@ -2518,24 +2545,112 @@
     <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="5"/>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
-      <c r="A15" s="6"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3"/>
     </row>
+    <row r="16" ht="16.5" spans="1:4">
+      <c r="A16" s="7"/>
+      <c r="B16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:4">
+      <c r="A17" s="7"/>
+      <c r="B17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:4">
+      <c r="A18" s="6"/>
+      <c r="B18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:4">
+      <c r="A20" s="5"/>
+      <c r="B20" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:4">
+      <c r="A21" s="5"/>
+      <c r="B21" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:4">
+      <c r="A22" s="7"/>
+      <c r="B22" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:4">
+      <c r="A23" s="7"/>
+      <c r="B23" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:4">
+      <c r="A25" s="5"/>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:4">
+      <c r="A26" s="5"/>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:4">
+      <c r="A27" s="7"/>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:4">
+      <c r="A28" s="7"/>
+      <c r="B28" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="A24:A28"/>
     <mergeCell ref="B4:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="152">
   <si>
     <t>一级菜单</t>
   </si>
@@ -1213,7 +1213,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1229,9 +1229,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1595,12 +1592,12 @@
   <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7545454545455" style="8" customWidth="1"/>
-    <col min="2" max="2" width="22.1272727272727" style="8" customWidth="1"/>
-    <col min="3" max="3" width="27.3727272727273" style="8" customWidth="1"/>
-    <col min="4" max="4" width="126.818181818182" style="9" customWidth="1"/>
-    <col min="5" max="5" width="10.4545454545455" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
+    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
@@ -1630,10 +1627,10 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2"/>
@@ -1641,10 +1638,10 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="2"/>
@@ -1654,10 +1651,10 @@
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="2"/>
@@ -1665,10 +1662,10 @@
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="2"/>
@@ -1678,10 +1675,10 @@
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="2"/>
@@ -1689,10 +1686,10 @@
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="2"/>
@@ -1700,10 +1697,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="2"/>
@@ -1711,10 +1708,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="2"/>
@@ -1722,10 +1719,10 @@
         <v>25</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="2"/>
@@ -1733,10 +1730,10 @@
         <v>27</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -1746,7 +1743,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="3"/>
@@ -1757,10 +1754,10 @@
         <v>32</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="11"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="2"/>
@@ -1768,7 +1765,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="3"/>
@@ -1779,7 +1776,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
@@ -1790,7 +1787,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E16" s="3"/>
@@ -1801,7 +1798,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E17" s="3"/>
@@ -1812,7 +1809,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="3"/>
@@ -1823,7 +1820,7 @@
         <v>44</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="3"/>
@@ -1836,7 +1833,7 @@
         <v>47</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3"/>
@@ -1847,10 +1844,10 @@
         <v>49</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="5"/>
@@ -1858,10 +1855,10 @@
         <v>51</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="5"/>
@@ -1869,10 +1866,10 @@
         <v>53</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="5"/>
@@ -1880,10 +1877,10 @@
         <v>55</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="11"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="5"/>
@@ -1891,10 +1888,10 @@
         <v>57</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="6"/>
@@ -1902,10 +1899,10 @@
         <v>59</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="2" t="s">
@@ -1915,7 +1912,7 @@
         <v>62</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E27" s="3"/>
@@ -1926,7 +1923,7 @@
         <v>64</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="s">
         <v>65</v>
       </c>
       <c r="E28" s="3"/>
@@ -1937,7 +1934,7 @@
         <v>66</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E29" s="3"/>
@@ -1948,7 +1945,7 @@
         <v>68</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="9" t="s">
         <v>69</v>
       </c>
       <c r="E30" s="3"/>
@@ -1959,7 +1956,7 @@
         <v>70</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="12" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="3"/>
@@ -1970,7 +1967,7 @@
         <v>72</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="3"/>
@@ -1983,7 +1980,7 @@
         <v>75</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="12" t="s">
         <v>76</v>
       </c>
       <c r="E33" s="3"/>
@@ -1994,7 +1991,7 @@
         <v>77</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>78</v>
       </c>
       <c r="E34" s="3"/>
@@ -2005,7 +2002,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>80</v>
       </c>
       <c r="E35" s="3"/>
@@ -2016,7 +2013,7 @@
         <v>81</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E36" s="3"/>
@@ -2027,7 +2024,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="12" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="3"/>
@@ -2038,7 +2035,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E38" s="3"/>
@@ -2053,7 +2050,7 @@
       <c r="C39" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E39" s="3"/>
@@ -2064,7 +2061,7 @@
       <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="9" t="s">
         <v>92</v>
       </c>
       <c r="E40" s="3"/>
@@ -2075,7 +2072,7 @@
       <c r="C41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="9" t="s">
         <v>94</v>
       </c>
       <c r="E41" s="3"/>
@@ -2088,7 +2085,7 @@
       <c r="C42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E42" s="3"/>
@@ -2099,7 +2096,7 @@
       <c r="C43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E43" s="3"/>
@@ -2110,7 +2107,7 @@
       <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="9" t="s">
         <v>101</v>
       </c>
       <c r="E44" s="3"/>
@@ -2121,7 +2118,7 @@
       <c r="C45" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>103</v>
       </c>
       <c r="E45" s="3"/>
@@ -2134,7 +2131,7 @@
       <c r="C46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="9" t="s">
         <v>106</v>
       </c>
       <c r="E46" s="3"/>
@@ -2145,7 +2142,7 @@
       <c r="C47" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E47" s="3"/>
@@ -2158,7 +2155,7 @@
       <c r="C48" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E48" s="3"/>
@@ -2169,7 +2166,7 @@
       <c r="C49" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E49" s="3"/>
@@ -2180,7 +2177,7 @@
       <c r="C50" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="9" t="s">
         <v>115</v>
       </c>
       <c r="E50" s="3"/>
@@ -2193,7 +2190,7 @@
         <v>117</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="9" t="s">
         <v>118</v>
       </c>
       <c r="E51" s="3"/>
@@ -2203,8 +2200,8 @@
       <c r="B52" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10" t="s">
+      <c r="C52" s="9"/>
+      <c r="D52" s="9" t="s">
         <v>120</v>
       </c>
       <c r="E52" s="3"/>
@@ -2214,8 +2211,8 @@
       <c r="B53" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10" t="s">
+      <c r="C53" s="9"/>
+      <c r="D53" s="9" t="s">
         <v>122</v>
       </c>
       <c r="E53" s="3"/>
@@ -2227,8 +2224,8 @@
       <c r="B54" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
       <c r="E54" s="3"/>
     </row>
     <row r="55" ht="16.5" spans="1:5">
@@ -2236,8 +2233,8 @@
       <c r="B55" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
       <c r="E55" s="3"/>
     </row>
     <row r="56" ht="16.5" spans="1:5">
@@ -2245,8 +2242,8 @@
       <c r="B56" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
       <c r="E56" s="3"/>
     </row>
     <row r="57" ht="16.5" spans="1:5">
@@ -2254,8 +2251,8 @@
       <c r="B57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
       <c r="E57" s="3"/>
     </row>
     <row r="58" ht="16.5" spans="1:5">
@@ -2265,8 +2262,8 @@
       <c r="B58" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
       <c r="E58" s="3"/>
     </row>
     <row r="59" ht="16.5" spans="1:5">
@@ -2275,7 +2272,7 @@
         <v>130</v>
       </c>
       <c r="C59" s="2"/>
-      <c r="D59" s="10"/>
+      <c r="D59" s="9"/>
       <c r="E59" s="3"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
@@ -2284,7 +2281,7 @@
         <v>131</v>
       </c>
       <c r="C60" s="2"/>
-      <c r="D60" s="10"/>
+      <c r="D60" s="9"/>
       <c r="E60" s="3"/>
     </row>
     <row r="61" ht="16.5" spans="1:5">
@@ -2293,7 +2290,7 @@
         <v>132</v>
       </c>
       <c r="C61" s="2"/>
-      <c r="D61" s="10"/>
+      <c r="D61" s="9"/>
       <c r="E61" s="3"/>
     </row>
     <row r="62" ht="16.5" spans="1:5">
@@ -2302,7 +2299,7 @@
         <v>133</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="10"/>
+      <c r="D62" s="9"/>
       <c r="E62" s="3"/>
     </row>
     <row r="63" ht="16.5" spans="1:5">
@@ -2311,7 +2308,7 @@
         <v>134</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="10"/>
+      <c r="D63" s="9"/>
       <c r="E63" s="3"/>
     </row>
     <row r="64" ht="16.5" spans="1:5">
@@ -2320,7 +2317,7 @@
         <v>135</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="10"/>
+      <c r="D64" s="9"/>
       <c r="E64" s="3"/>
     </row>
     <row r="65" ht="16.5" spans="1:5">
@@ -2329,7 +2326,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="10"/>
+      <c r="D65" s="9"/>
       <c r="E65" s="3"/>
     </row>
     <row r="66" ht="16.5" spans="1:5">
@@ -2338,7 +2335,7 @@
         <v>137</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="10"/>
+      <c r="D66" s="9"/>
       <c r="E66" s="3"/>
     </row>
     <row r="67" ht="16.5" spans="1:5">
@@ -2347,7 +2344,7 @@
         <v>138</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="9"/>
       <c r="E67" s="3"/>
     </row>
     <row r="68" ht="16.5" spans="1:5">
@@ -2356,7 +2353,7 @@
         <v>139</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="10"/>
+      <c r="D68" s="9"/>
       <c r="E68" s="3"/>
     </row>
   </sheetData>
@@ -2561,7 +2558,7 @@
       <c r="D15" s="3"/>
     </row>
     <row r="16" ht="16.5" spans="1:4">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="2" t="s">
         <v>145</v>
       </c>
@@ -2571,7 +2568,7 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
-      <c r="A17" s="7"/>
+      <c r="A17" s="5"/>
       <c r="B17" s="2" t="s">
         <v>146</v>
       </c>
@@ -2595,54 +2592,84 @@
       <c r="B19" s="2" t="s">
         <v>126</v>
       </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="5"/>
       <c r="B20" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
       <c r="A21" s="5"/>
       <c r="B21" s="2" t="s">
         <v>124</v>
       </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
-      <c r="A22" s="7"/>
+      <c r="A22" s="5"/>
       <c r="B22" s="2" t="s">
         <v>125</v>
       </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
-      <c r="A23" s="7"/>
+      <c r="A23" s="5"/>
       <c r="B23" s="2" t="s">
         <v>149</v>
       </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" ht="16.5" spans="1:4">
-      <c r="A25" s="5"/>
+      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" ht="16.5" spans="1:4">
-      <c r="A26" s="5"/>
+      <c r="A26" s="2"/>
       <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" ht="16.5" spans="1:4">
-      <c r="A27" s="7"/>
+      <c r="A27" s="2"/>
       <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" ht="16.5" spans="1:4">
-      <c r="A28" s="7"/>
+      <c r="A28" s="2"/>
       <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/doc/设计文档/功能设计/功能清单.xlsx
+++ b/doc/设计文档/功能设计/功能清单.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12200" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="11750" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="清单" sheetId="3" r:id="rId1"/>
     <sheet name="一阶段" sheetId="4" r:id="rId2"/>
+    <sheet name="二阶段" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="159">
   <si>
     <t>一级菜单</t>
   </si>
@@ -483,6 +484,9 @@
     <t>产品BOM</t>
   </si>
   <si>
+    <t>工作站</t>
+  </si>
+  <si>
     <t>物料清单</t>
   </si>
   <si>
@@ -511,6 +515,24 @@
   </si>
   <si>
     <t>考勤记录</t>
+  </si>
+  <si>
+    <t>打卡规则</t>
+  </si>
+  <si>
+    <t>流程管理</t>
+  </si>
+  <si>
+    <t>集成</t>
+  </si>
+  <si>
+    <t>任务管理</t>
+  </si>
+  <si>
+    <t>及时通讯</t>
+  </si>
+  <si>
+    <t>优化/完成情况</t>
   </si>
 </sst>
 </file>
@@ -1213,19 +1235,28 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1592,12 +1623,12 @@
   <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7545454545455" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.1272727272727" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.3727272727273" style="7" customWidth="1"/>
-    <col min="4" max="4" width="126.818181818182" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.4545454545455" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="13.7545454545455" style="10" customWidth="1"/>
+    <col min="2" max="2" width="22.1272727272727" style="10" customWidth="1"/>
+    <col min="3" max="3" width="27.3727272727273" style="10" customWidth="1"/>
+    <col min="4" max="4" width="126.818181818182" style="11" customWidth="1"/>
+    <col min="5" max="5" width="10.4545454545455" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
@@ -1618,743 +1649,743 @@
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" ht="16.5" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" ht="16.5" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" ht="16.5" spans="1:5">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" ht="16.5" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" ht="16.5" spans="1:5">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" ht="16.5" spans="1:5">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" ht="16.5" spans="1:5">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" ht="16.5" spans="1:5">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="9" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="3"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" ht="16.5" spans="1:5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="3"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="3"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="3"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="9" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="3"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="5"/>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="5"/>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="9" t="s">
+      <c r="C22" s="3"/>
+      <c r="D22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="5"/>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="3"/>
+      <c r="D23" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="10"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="5"/>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="9" t="s">
+      <c r="C24" s="3"/>
+      <c r="D24" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="10"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="5"/>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="7"/>
+      <c r="B25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="9" t="s">
+      <c r="C25" s="3"/>
+      <c r="D25" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="10"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="6"/>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="8"/>
+      <c r="B26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="3"/>
+      <c r="D26" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="10"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" ht="16.5" spans="1:5">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="9" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2" t="s">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="3"/>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="9" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="3"/>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2" t="s">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="9" t="s">
+      <c r="C30" s="3"/>
+      <c r="D30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E30" s="3"/>
+      <c r="E30" s="4"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="12" t="s">
+      <c r="C31" s="3"/>
+      <c r="D31" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="4"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="3"/>
+      <c r="D32" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="4"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="3"/>
+      <c r="D33" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="3"/>
+      <c r="E33" s="4"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="3"/>
+      <c r="D34" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="3"/>
+      <c r="E34" s="4"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="12" t="s">
+      <c r="C35" s="3"/>
+      <c r="D35" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="4"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2" t="s">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="12" t="s">
+      <c r="C36" s="3"/>
+      <c r="D36" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2" t="s">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="12" t="s">
+      <c r="C37" s="3"/>
+      <c r="D37" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="3"/>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2" t="s">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="12" t="s">
+      <c r="C38" s="3"/>
+      <c r="D38" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E38" s="3"/>
+      <c r="E38" s="4"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="3"/>
+      <c r="E39" s="4"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A40" s="2"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="2" t="s">
+      <c r="A40" s="3"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="4"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A41" s="2"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="2" t="s">
+      <c r="A41" s="3"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E41" s="3"/>
+      <c r="E41" s="4"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A42" s="2"/>
-      <c r="B42" s="4" t="s">
+      <c r="A42" s="3"/>
+      <c r="B42" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E42" s="3"/>
+      <c r="E42" s="4"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A43" s="2"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="2" t="s">
+      <c r="A43" s="3"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="3"/>
+      <c r="E43" s="4"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A44" s="2"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="2" t="s">
+      <c r="A44" s="3"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="3"/>
+      <c r="E44" s="4"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A45" s="2"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="2" t="s">
+      <c r="A45" s="3"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A46" s="2"/>
-      <c r="B46" s="4" t="s">
+      <c r="A46" s="3"/>
+      <c r="B46" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="E46" s="3"/>
+      <c r="E46" s="4"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A47" s="2"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="2" t="s">
+      <c r="A47" s="3"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E47" s="3"/>
+      <c r="E47" s="4"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A48" s="2"/>
-      <c r="B48" s="4" t="s">
+      <c r="A48" s="3"/>
+      <c r="B48" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="3"/>
+      <c r="E48" s="4"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A49" s="2"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="2" t="s">
+      <c r="A49" s="3"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E49" s="3"/>
+      <c r="E49" s="4"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A50" s="2"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="2" t="s">
+      <c r="A50" s="3"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="E50" s="3"/>
+      <c r="E50" s="4"/>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="9" t="s">
+      <c r="C51" s="3"/>
+      <c r="D51" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E51" s="3"/>
+      <c r="E51" s="4"/>
     </row>
     <row r="52" ht="16.5" spans="1:5">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2" t="s">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9" t="s">
+      <c r="C52" s="12"/>
+      <c r="D52" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="E52" s="3"/>
+      <c r="E52" s="4"/>
     </row>
     <row r="53" ht="16.5" spans="1:5">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9" t="s">
+      <c r="C53" s="12"/>
+      <c r="D53" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="E53" s="3"/>
+      <c r="E53" s="4"/>
     </row>
     <row r="54" ht="16.5" spans="1:5">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="3"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="4"/>
     </row>
     <row r="55" ht="16.5" spans="1:5">
-      <c r="A55" s="5"/>
-      <c r="B55" s="2" t="s">
+      <c r="A55" s="7"/>
+      <c r="B55" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="3"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="4"/>
     </row>
     <row r="56" ht="16.5" spans="1:5">
-      <c r="A56" s="5"/>
-      <c r="B56" s="2" t="s">
+      <c r="A56" s="7"/>
+      <c r="B56" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="3"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="4"/>
     </row>
     <row r="57" ht="16.5" spans="1:5">
-      <c r="A57" s="6"/>
-      <c r="B57" s="2" t="s">
+      <c r="A57" s="8"/>
+      <c r="B57" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="3"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="4"/>
     </row>
     <row r="58" ht="16.5" spans="1:5">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="3"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="4"/>
     </row>
     <row r="59" ht="16.5" spans="1:5">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2" t="s">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="4"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2" t="s">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="4"/>
     </row>
     <row r="61" ht="16.5" spans="1:5">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2" t="s">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" ht="16.5" spans="1:5">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2" t="s">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" ht="16.5" spans="1:5">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2" t="s">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="4"/>
     </row>
     <row r="64" ht="16.5" spans="1:5">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2" t="s">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="4"/>
     </row>
     <row r="65" ht="16.5" spans="1:5">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="4"/>
     </row>
     <row r="66" ht="16.5" spans="1:5">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2" t="s">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="4"/>
     </row>
     <row r="67" ht="16.5" spans="1:5">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2" t="s">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="4"/>
     </row>
     <row r="68" ht="16.5" spans="1:5">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2" t="s">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2384,7 +2415,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
@@ -2411,273 +2442,641 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
-      <c r="A5" s="2"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:4">
-      <c r="A6" s="2"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:4">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="4" t="s">
         <v>140</v>
       </c>
     </row>
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:4">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:4">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:4">
+      <c r="A17" s="7"/>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:4">
+      <c r="A18" s="7"/>
+      <c r="B18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:4">
+      <c r="A19" s="7"/>
+      <c r="B19" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:4">
+      <c r="A20" s="7"/>
+      <c r="B20" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:4">
+      <c r="A21" s="8"/>
+      <c r="B21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:4">
+      <c r="A22" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:4">
+      <c r="A23" s="7"/>
+      <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:4">
+      <c r="A24" s="7"/>
+      <c r="B24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:4">
+      <c r="A25" s="7"/>
+      <c r="B25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:4">
+      <c r="A26" s="7"/>
+      <c r="B26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:4">
+      <c r="A28" s="9"/>
+      <c r="B28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:4">
+      <c r="A30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:4">
+      <c r="A31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B4:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="20.0909090909091" customWidth="1"/>
+    <col min="2" max="2" width="30.3636363636364" customWidth="1"/>
+    <col min="3" max="3" width="16.0909090909091" customWidth="1"/>
+    <col min="4" max="4" width="20.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:4">
+      <c r="A3" s="5"/>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:4">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:4">
+      <c r="A5" s="5"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:4">
+      <c r="A6" s="5"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:4">
+      <c r="A7" s="5"/>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:4">
+      <c r="A8" s="5"/>
+      <c r="B8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+    </row>
     <row r="9" ht="16.5" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:4">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:4">
-      <c r="A13" s="4" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:4">
+      <c r="A16" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:4">
-      <c r="A14" s="5"/>
-      <c r="B14" s="2" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:4">
+      <c r="A17" s="7"/>
+      <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:4">
-      <c r="A15" s="5"/>
-      <c r="B15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:4">
-      <c r="A16" s="5"/>
-      <c r="B16" s="2" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:4">
+      <c r="A18" s="7"/>
+      <c r="B18" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:4">
-      <c r="A17" s="5"/>
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:4">
+      <c r="A19" s="7"/>
+      <c r="B19" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:4">
-      <c r="A18" s="6"/>
-      <c r="B18" s="2" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:4">
+      <c r="A20" s="7"/>
+      <c r="B20" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:4">
+      <c r="A21" s="8"/>
+      <c r="B21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:4">
+      <c r="A22" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:4">
-      <c r="A20" s="5"/>
-      <c r="B20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:4">
-      <c r="A21" s="5"/>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:4">
+      <c r="A23" s="7"/>
+      <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:4">
+      <c r="A24" s="7"/>
+      <c r="B24" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:4">
-      <c r="A22" s="5"/>
-      <c r="B22" s="2" t="s">
+      <c r="C24" s="3"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:4">
+      <c r="A25" s="7"/>
+      <c r="B25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:4">
-      <c r="A23" s="5"/>
-      <c r="B23" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="C25" s="3"/>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:4">
+      <c r="A26" s="7"/>
+      <c r="B26" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:4">
+      <c r="A27" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:4">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:4">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:4">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="B27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" ht="16.5" spans="1:4">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:4">
+      <c r="A30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:4">
+      <c r="A31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:4">
+      <c r="A32" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:1">
+      <c r="A33" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A19:A23"/>
-    <mergeCell ref="A24:A28"/>
+  <mergeCells count="7">
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A27:A28"/>
     <mergeCell ref="B4:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
